--- a/00_SBG/07_ライブラリ/外部資料/sample_Ver.0.20.xlsx
+++ b/00_SBG/07_ライブラリ/外部資料/sample_Ver.0.20.xlsx
@@ -5,13 +5,13 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\playn\Documents\Github\-Obsidian\SBG\00_SBG\07_ライブラリ\外部資料\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\payla\Documents\GitHub\SBG_Obsidian\00_SBG\07_ライブラリ\外部資料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC73B9D4-EA56-4373-B0E0-8255BAE68B75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{480DCE62-9B66-4199-96AD-2D8A6511163E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="14016" windowHeight="13056" firstSheet="12" activeTab="14" xr2:uid="{CC877802-03BC-4969-A51E-B94D651D550E}"/>
-    <workbookView xWindow="13728" yWindow="0" windowWidth="9408" windowHeight="13056" firstSheet="8" activeTab="8" xr2:uid="{F2E714A0-CDCB-4184-8BAB-EA611DA3D625}"/>
+    <workbookView xWindow="-110" yWindow="-10910" windowWidth="19420" windowHeight="11020" firstSheet="3" activeTab="5" xr2:uid="{F2E714A0-CDCB-4184-8BAB-EA611DA3D625}"/>
+    <workbookView xWindow="-19310" yWindow="-10930" windowWidth="19420" windowHeight="11020" firstSheet="8" activeTab="12" xr2:uid="{1AFB224D-C5F6-4405-A264-ECF4615FFB57}"/>
   </bookViews>
   <sheets>
     <sheet name="Character" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="229">
   <si>
     <t>Name</t>
   </si>
@@ -470,10 +470,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ヒーラーバフ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>FlagImmediately</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -648,9 +644,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ENBバフ2_綾瀬心音</t>
-  </si>
-  <si>
     <t>ENBバフ3_綾瀬心音</t>
   </si>
   <si>
@@ -815,13 +808,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ENBバフ2_東雲倫</t>
-    <rPh sb="7" eb="10">
-      <t>シノノメリン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ENBバフ3_東雲倫</t>
     <rPh sb="7" eb="10">
       <t>シノノメリン</t>
@@ -887,6 +873,357 @@
   <si>
     <t>必殺連撃_バフ</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>白鷺彩</t>
+  </si>
+  <si>
+    <t>千堂美樹</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>白鷺彩</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>夜見塔子</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ガラナB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>合気道</t>
+    <rPh sb="0" eb="3">
+      <t>アイキドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>黒塗りドス</t>
+    <rPh sb="0" eb="2">
+      <t>クロヌ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>霧島梓</t>
+  </si>
+  <si>
+    <t>軍人E</t>
+    <rPh sb="0" eb="2">
+      <t>グンジン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スタンガンスマホ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>パドル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>東雲倫,千堂美樹,霧島梓</t>
+    <rPh sb="0" eb="2">
+      <t>シノノメ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>リン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>キリシマ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>アズサ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>綾瀬心音,夜見塔子</t>
+    <rPh sb="0" eb="2">
+      <t>アヤセ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ココロ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>オト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>白鷺彩,スズキカナエ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>混乱(小)</t>
+    <rPh sb="0" eb="2">
+      <t>コンラン</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>興奮(小)</t>
+    <rPh sb="0" eb="2">
+      <t>コウフン</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>魅了(小)</t>
+    <rPh sb="0" eb="2">
+      <t>ミリョウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>P4</t>
+  </si>
+  <si>
+    <t>P5</t>
+  </si>
+  <si>
+    <t>P6</t>
+  </si>
+  <si>
+    <t>P7</t>
+  </si>
+  <si>
+    <t>P8</t>
+  </si>
+  <si>
+    <t>夜見塔子(敵)</t>
+    <rPh sb="5" eb="6">
+      <t>テキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>霧島梓(敵)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スズキカナエ(敵)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>才能軍人E</t>
+    <rPh sb="2" eb="4">
+      <t>グンジン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>才能_夜見塔子(敵)</t>
+    <rPh sb="0" eb="2">
+      <t>サイノウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ヨミ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>テキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>才能_霧島梓(敵)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>才能_スズキカナエ(敵)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>才能開花1_千堂美樹</t>
+    <rPh sb="0" eb="4">
+      <t>サイノウカイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>才能開花2_千堂美樹</t>
+    <rPh sb="0" eb="4">
+      <t>サイノウカイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>才能開花3_千堂美樹</t>
+    <rPh sb="0" eb="4">
+      <t>サイノウカイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>才能開花1_白鷺彩</t>
+    <rPh sb="0" eb="4">
+      <t>サイノウカイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>才能開花2_白鷺彩</t>
+    <rPh sb="0" eb="4">
+      <t>サイノウカイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>才能開花3_白鷺彩</t>
+    <rPh sb="0" eb="4">
+      <t>サイノウカイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ENBバフ1_千堂美樹</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ENBバフ3_千堂美樹</t>
+  </si>
+  <si>
+    <t>ENBバフ1_白鷺彩</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ENBバフ3_白鷺彩</t>
+  </si>
+  <si>
+    <t>一気呵成</t>
+    <rPh sb="0" eb="4">
+      <t>イッキカセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>義勇任侠</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>兵站</t>
+    <rPh sb="0" eb="2">
+      <t>ヘイタン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ANFTMN</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>軍人E</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ラリアット_攻撃</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ラリアット_バフ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>薬品散布_攻撃</t>
+    <rPh sb="0" eb="2">
+      <t>ヤクヒン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>サンプ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>薬品散布_バフ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>一文字_攻撃</t>
+    <rPh sb="0" eb="3">
+      <t>イチモンジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>一文字_バフ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サイドアーム_攻撃</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サイドアーム_バフ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>改造フラッシュ_攻撃</t>
+    <rPh sb="0" eb="2">
+      <t>カイゾウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>改造フラッシュ_バフ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>混乱(小)デバフ</t>
+    <rPh sb="0" eb="2">
+      <t>コンラン</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>興奮(小)デバフ</t>
+    <rPh sb="0" eb="2">
+      <t>コウフン</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>魅了(小)デバフ</t>
+    <rPh sb="0" eb="2">
+      <t>ミリョウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ラリアット</t>
+  </si>
+  <si>
+    <t>薬品散布</t>
+  </si>
+  <si>
+    <t>一文字</t>
+  </si>
+  <si>
+    <t>サイドアーム</t>
+  </si>
+  <si>
+    <t>改造フラッシュ</t>
   </si>
 </sst>
 </file>
@@ -955,7 +1292,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -968,30 +1305,14 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="6">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="游ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="none">
@@ -1049,6 +1370,25 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1063,7 +1403,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C6559B23-0835-462E-B656-3418C5C0ED20}" name="Character" displayName="Character" ref="A1:Q7" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C6559B23-0835-462E-B656-3418C5C0ED20}" name="Character" displayName="Character" ref="A1:Q13" totalsRowShown="0">
   <tableColumns count="17">
     <tableColumn id="1" xr3:uid="{F7FB57F2-50EE-440C-B562-F5C2505D5A99}" name="Name"/>
     <tableColumn id="2" xr3:uid="{22BA3C11-E50E-40CC-ABC9-A7A6FDF9F292}" name="TeamOrder"/>
@@ -1098,7 +1438,7 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{FA0A0C0E-CB09-4A0D-994E-CC837828F769}" name="テーブル10" displayName="テーブル10" ref="A1:C10" totalsRowShown="0" headerRowDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{FA0A0C0E-CB09-4A0D-994E-CC837828F769}" name="テーブル10" displayName="テーブル10" ref="A1:C10" totalsRowShown="0" headerRowDxfId="5">
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{4EC8B85D-183E-4D85-9F17-3A16F9A8CC8F}" name="AttributeAtk"/>
     <tableColumn id="2" xr3:uid="{45C61E5D-7816-4402-B480-43C44FF1F508}" name="AttributeDef"/>
@@ -1120,11 +1460,11 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{F45502FC-BDD8-4732-AF30-F77FCFC85D67}" name="テーブル14" displayName="テーブル14" ref="A1:C5" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{F45502FC-BDD8-4732-AF30-F77FCFC85D67}" name="テーブル14" displayName="テーブル14" ref="A1:C6" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{281706EF-DF9D-4DFD-809F-D4BFAF60DF88}" name="InflictStatusName" dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{7CD90233-A590-4098-B6C8-1757FF316C7D}" name="ApplyRate" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{6EFF2D66-3E39-4B8C-94DE-137C376623B3}" name="BuffName" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{281706EF-DF9D-4DFD-809F-D4BFAF60DF88}" name="InflictStatusName" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{7CD90233-A590-4098-B6C8-1757FF316C7D}" name="ApplyRate" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{6EFF2D66-3E39-4B8C-94DE-137C376623B3}" name="BuffName" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1141,7 +1481,7 @@
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{7776C031-26DE-4DC8-8062-42DA5BB429C3}" name="テーブル15" displayName="テーブル15" ref="A1:Y37" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{7776C031-26DE-4DC8-8062-42DA5BB429C3}" name="テーブル15" displayName="テーブル15" ref="A1:Y48" totalsRowShown="0">
   <tableColumns count="25">
     <tableColumn id="1" xr3:uid="{8A4A6A4A-A2C5-490C-9909-EB90A76775C8}" name="Name"/>
     <tableColumn id="2" xr3:uid="{2F582D45-C691-4D5D-B102-31555EDE371D}" name="AtkBuff"/>
@@ -1186,7 +1526,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{F628C0A6-C856-47B5-95BB-E1CBCFFFACBD}" name="テーブル2" displayName="テーブル2" ref="A1:F6" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{F628C0A6-C856-47B5-95BB-E1CBCFFFACBD}" name="テーブル2" displayName="テーブル2" ref="A1:F11" totalsRowShown="0">
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{7342D2A0-A433-4EA7-9E2C-D148AC598B8D}" name="Name"/>
     <tableColumn id="2" xr3:uid="{B14A8ABC-4D0B-41DF-8DA2-A05E4C86DF46}" name="HPPoint"/>
@@ -1213,7 +1553,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{EDAA588E-A448-44CD-AC57-3CF00A25A8D8}" name="テーブル4" displayName="テーブル4" ref="A1:C7" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{EDAA588E-A448-44CD-AC57-3CF00A25A8D8}" name="テーブル4" displayName="テーブル4" ref="A1:C13" totalsRowShown="0">
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{F471E044-3C40-448A-AABF-2F51CE4F7C23}" name="CharacterName"/>
     <tableColumn id="2" xr3:uid="{9BF376ED-0CF3-47BB-8DC0-62D56439964E}" name="Category"/>
@@ -1249,7 +1589,7 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{D5C7C08F-BDDB-42A7-B70E-107F2B4F8E91}" name="テーブル7" displayName="テーブル7" ref="A1:H11" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{D5C7C08F-BDDB-42A7-B70E-107F2B4F8E91}" name="テーブル7" displayName="テーブル7" ref="A1:H21" totalsRowShown="0">
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{C2276B14-94AC-4936-8F2B-276821846D39}" name="Name"/>
     <tableColumn id="2" xr3:uid="{BDE637FF-B1EC-4984-AED6-0E0E51577C2D}" name="Talent"/>
@@ -1265,7 +1605,7 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{A4DE3E32-0DCE-424B-B13A-7796466AF57A}" name="テーブル8" displayName="テーブル8" ref="A1:F11" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{A4DE3E32-0DCE-424B-B13A-7796466AF57A}" name="テーブル8" displayName="テーブル8" ref="A1:F17" totalsRowShown="0">
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{232FEBDF-5D2D-4648-806B-5BD94955CCE3}" name="Name"/>
     <tableColumn id="2" xr3:uid="{E02A021D-57D9-4E1D-A02D-20E20F56BE76}" name="CharacterName"/>
@@ -1575,27 +1915,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55B8B1C1-796A-41F2-87F3-C69DB116ED24}">
-  <dimension ref="A1:Q12"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:Q18"/>
+  <sheetFormatPr defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.7"/>
   <cols>
-    <col min="1" max="1" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.09765625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.3984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.3984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.69921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.6875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="16" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.8984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.8984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="27.5" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="18.09765625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1648,15 +1988,15 @@
         <v>94</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.7">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
         <v>2</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
       </c>
       <c r="D2" t="b">
         <v>1</v>
@@ -1665,16 +2005,16 @@
         <v>999999</v>
       </c>
       <c r="F2">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="G2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I2" t="s">
-        <v>146</v>
+        <v>104</v>
       </c>
       <c r="J2">
         <v>50</v>
@@ -1683,16 +2023,16 @@
         <v>2</v>
       </c>
       <c r="L2">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="M2">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="N2">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="O2">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -1701,15 +2041,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.7">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3" t="b">
         <v>1</v>
@@ -1718,16 +2058,16 @@
         <v>999999</v>
       </c>
       <c r="F3">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="G3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I3" t="s">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="J3">
         <v>50</v>
@@ -1736,16 +2076,16 @@
         <v>2</v>
       </c>
       <c r="L3">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="M3">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="N3">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="O3">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="P3">
         <v>0</v>
@@ -1754,51 +2094,51 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.7">
       <c r="A4" t="s">
-        <v>103</v>
+        <v>168</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4">
         <v>999999</v>
       </c>
       <c r="F4">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="G4">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I4" t="s">
-        <v>151</v>
+        <v>172</v>
       </c>
       <c r="J4">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="K4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L4">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="M4">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="N4">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="P4">
         <v>0</v>
@@ -1807,51 +2147,51 @@
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.7">
       <c r="A5" t="s">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
         <v>2</v>
       </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
       <c r="D5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5">
         <v>999999</v>
       </c>
       <c r="F5">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="G5">
+        <v>8</v>
+      </c>
+      <c r="H5">
         <v>6</v>
       </c>
-      <c r="H5">
+      <c r="I5" t="s">
+        <v>171</v>
+      </c>
+      <c r="J5">
+        <v>50</v>
+      </c>
+      <c r="K5">
         <v>2</v>
-      </c>
-      <c r="I5" t="s">
-        <v>152</v>
-      </c>
-      <c r="J5">
-        <v>65</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
       </c>
       <c r="L5">
         <v>0.1</v>
       </c>
       <c r="M5">
+        <v>1.4</v>
+      </c>
+      <c r="N5">
+        <v>0.3</v>
+      </c>
+      <c r="O5">
         <v>1.3</v>
-      </c>
-      <c r="N5">
-        <v>0.15</v>
-      </c>
-      <c r="O5">
-        <v>0</v>
       </c>
       <c r="P5">
         <v>0</v>
@@ -1860,15 +2200,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.7">
       <c r="A6" t="s">
-        <v>138</v>
+        <v>189</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6" t="b">
         <v>0</v>
@@ -1877,34 +2217,34 @@
         <v>999999</v>
       </c>
       <c r="F6">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="G6">
+        <v>13</v>
+      </c>
+      <c r="H6">
         <v>4</v>
       </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
       <c r="I6" t="s">
-        <v>151</v>
+        <v>173</v>
       </c>
       <c r="J6">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="K6">
         <v>1</v>
       </c>
       <c r="L6">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
       <c r="M6">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="N6">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="P6">
         <v>0</v>
@@ -1913,15 +2253,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.7">
       <c r="A7" t="s">
-        <v>139</v>
+        <v>190</v>
       </c>
       <c r="B7">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" t="b">
         <v>0</v>
@@ -1930,34 +2270,34 @@
         <v>999999</v>
       </c>
       <c r="F7">
+        <v>90</v>
+      </c>
+      <c r="G7">
+        <v>12</v>
+      </c>
+      <c r="H7">
+        <v>5</v>
+      </c>
+      <c r="I7" t="s">
+        <v>177</v>
+      </c>
+      <c r="J7">
         <v>30</v>
       </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-      <c r="H7">
-        <v>3</v>
-      </c>
-      <c r="I7" t="s">
-        <v>153</v>
-      </c>
-      <c r="J7">
-        <v>60</v>
-      </c>
       <c r="K7">
         <v>1</v>
       </c>
       <c r="L7">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="M7">
         <v>1.3</v>
       </c>
       <c r="N7">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -1966,8 +2306,326 @@
         <v>100</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="C12" s="2"/>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.7">
+      <c r="A8" t="s">
+        <v>191</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>2</v>
+      </c>
+      <c r="D8" t="b">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>999999</v>
+      </c>
+      <c r="F8">
+        <v>65</v>
+      </c>
+      <c r="G8">
+        <v>9</v>
+      </c>
+      <c r="H8">
+        <v>7</v>
+      </c>
+      <c r="I8" t="s">
+        <v>176</v>
+      </c>
+      <c r="J8">
+        <v>30</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <v>0.05</v>
+      </c>
+      <c r="M8">
+        <v>1.5</v>
+      </c>
+      <c r="N8">
+        <v>0.3</v>
+      </c>
+      <c r="O8">
+        <v>1.35</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.7">
+      <c r="A9" t="s">
+        <v>102</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9" t="b">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>999999</v>
+      </c>
+      <c r="F9">
+        <v>35</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9" t="s">
+        <v>149</v>
+      </c>
+      <c r="J9">
+        <v>65</v>
+      </c>
+      <c r="K9">
+        <v>1</v>
+      </c>
+      <c r="L9">
+        <v>0.1</v>
+      </c>
+      <c r="M9">
+        <v>1.3</v>
+      </c>
+      <c r="N9">
+        <v>0.2</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.7">
+      <c r="A10" t="s">
+        <v>103</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10" t="b">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>999999</v>
+      </c>
+      <c r="F10">
+        <v>40</v>
+      </c>
+      <c r="G10">
+        <v>6</v>
+      </c>
+      <c r="H10">
+        <v>2</v>
+      </c>
+      <c r="I10" t="s">
+        <v>150</v>
+      </c>
+      <c r="J10">
+        <v>65</v>
+      </c>
+      <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="L10">
+        <v>0.1</v>
+      </c>
+      <c r="M10">
+        <v>1.3</v>
+      </c>
+      <c r="N10">
+        <v>0.15</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.7">
+      <c r="A11" t="s">
+        <v>136</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11">
+        <v>2</v>
+      </c>
+      <c r="D11" t="b">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>999999</v>
+      </c>
+      <c r="F11">
+        <v>25</v>
+      </c>
+      <c r="G11">
+        <v>4</v>
+      </c>
+      <c r="H11">
+        <v>2</v>
+      </c>
+      <c r="I11" t="s">
+        <v>149</v>
+      </c>
+      <c r="J11">
+        <v>60</v>
+      </c>
+      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="L11">
+        <v>0.15</v>
+      </c>
+      <c r="M11">
+        <v>1.3</v>
+      </c>
+      <c r="N11">
+        <v>0.1</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.7">
+      <c r="A12" t="s">
+        <v>137</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+      <c r="D12" t="b">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>999999</v>
+      </c>
+      <c r="F12">
+        <v>30</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+      <c r="H12">
+        <v>3</v>
+      </c>
+      <c r="I12" t="s">
+        <v>151</v>
+      </c>
+      <c r="J12">
+        <v>60</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="L12">
+        <v>0.2</v>
+      </c>
+      <c r="M12">
+        <v>1.3</v>
+      </c>
+      <c r="N12">
+        <v>0.1</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.7">
+      <c r="A13" t="s">
+        <v>175</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13">
+        <v>2</v>
+      </c>
+      <c r="D13" t="b">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>999999</v>
+      </c>
+      <c r="F13">
+        <v>35</v>
+      </c>
+      <c r="G13">
+        <v>3</v>
+      </c>
+      <c r="H13">
+        <v>4</v>
+      </c>
+      <c r="I13" t="s">
+        <v>150</v>
+      </c>
+      <c r="J13">
+        <v>60</v>
+      </c>
+      <c r="K13">
+        <v>1</v>
+      </c>
+      <c r="L13">
+        <v>0.15</v>
+      </c>
+      <c r="M13">
+        <v>1.3</v>
+      </c>
+      <c r="N13">
+        <v>0.1</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="3:3" x14ac:dyDescent="0.7">
+      <c r="C18" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -1981,13 +2639,13 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEE8DF46-D209-4D20-A42D-5A124B098697}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.7"/>
   <cols>
-    <col min="1" max="1" width="16.59765625" customWidth="1"/>
-    <col min="2" max="2" width="11.09765625" customWidth="1"/>
+    <col min="1" max="1" width="16.625" customWidth="1"/>
+    <col min="2" max="2" width="11.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A1" t="s">
         <v>38</v>
       </c>
@@ -1995,7 +2653,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A2" t="s">
         <v>41</v>
       </c>
@@ -2003,7 +2661,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -2011,7 +2669,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -2019,7 +2677,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -2027,7 +2685,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -2035,7 +2693,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -2043,7 +2701,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -2051,7 +2709,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
     </row>
@@ -2067,14 +2725,14 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4756A621-9C73-46F6-BCC6-EFA4C1E375C5}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.7"/>
   <cols>
-    <col min="1" max="1" width="13.59765625" customWidth="1"/>
-    <col min="2" max="2" width="13.69921875" customWidth="1"/>
-    <col min="3" max="3" width="7.59765625" customWidth="1"/>
+    <col min="1" max="1" width="13.625" customWidth="1"/>
+    <col min="2" max="2" width="13.6875" customWidth="1"/>
+    <col min="3" max="3" width="7.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A1" s="1" t="s">
         <v>55</v>
       </c>
@@ -2085,7 +2743,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A2" t="s">
         <v>31</v>
       </c>
@@ -2096,7 +2754,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A3" t="s">
         <v>31</v>
       </c>
@@ -2107,7 +2765,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A4" t="s">
         <v>31</v>
       </c>
@@ -2118,7 +2776,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A5" t="s">
         <v>32</v>
       </c>
@@ -2129,7 +2787,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A6" t="s">
         <v>32</v>
       </c>
@@ -2140,7 +2798,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A7" t="s">
         <v>32</v>
       </c>
@@ -2151,7 +2809,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A8" t="s">
         <v>33</v>
       </c>
@@ -2162,7 +2820,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A9" t="s">
         <v>33</v>
       </c>
@@ -2173,7 +2831,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A10" t="s">
         <v>33</v>
       </c>
@@ -2196,14 +2854,14 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45C69C40-D8C8-4D84-9DB2-2ED24622B6ED}">
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.7"/>
   <cols>
-    <col min="1" max="1" width="9.8984375" customWidth="1"/>
-    <col min="2" max="2" width="11.59765625" customWidth="1"/>
-    <col min="3" max="3" width="6.8984375" customWidth="1"/>
+    <col min="1" max="1" width="9.875" customWidth="1"/>
+    <col min="2" max="2" width="11.625" customWidth="1"/>
+    <col min="3" max="3" width="6.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.7">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -2214,7 +2872,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.7">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2225,7 +2883,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.7">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2236,10 +2894,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.7">
       <c r="A4" s="2"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.7">
       <c r="D6" s="2"/>
     </row>
   </sheetData>
@@ -2253,15 +2911,15 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D85222A2-312A-4ED7-934F-358F77FC3BC8}">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.7"/>
   <cols>
-    <col min="1" max="1" width="18.8984375" customWidth="1"/>
-    <col min="2" max="2" width="11.69921875" customWidth="1"/>
+    <col min="1" max="1" width="18.875" customWidth="1"/>
+    <col min="2" max="2" width="11.6875" customWidth="1"/>
     <col min="3" max="3" width="13.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A1" s="1" t="s">
         <v>61</v>
       </c>
@@ -2272,26 +2930,59 @@
         <v>63</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B2">
         <v>0.2</v>
       </c>
       <c r="C2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B3">
         <v>0.3</v>
       </c>
       <c r="C3" t="s">
-        <v>128</v>
+        <v>127</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B4">
+        <v>0.25</v>
+      </c>
+      <c r="C4" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A5" t="s">
+        <v>182</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.3</v>
+      </c>
+      <c r="C5" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A6" t="s">
+        <v>183</v>
+      </c>
+      <c r="B6">
+        <v>0.2</v>
+      </c>
+      <c r="C6" t="s">
+        <v>223</v>
       </c>
     </row>
   </sheetData>
@@ -2306,31 +2997,31 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CEAA3CD-9992-44D9-9B4B-D14DBC9A2B99}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.7"/>
   <cols>
-    <col min="1" max="1" width="11.59765625" customWidth="1"/>
+    <col min="1" max="1" width="11.625" customWidth="1"/>
     <col min="2" max="2" width="16.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A1" t="s">
         <v>45</v>
       </c>
       <c r="B1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B3" t="b">
         <v>0</v>
@@ -2347,36 +3038,36 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8E5DC47-9D66-441C-BA5C-D7967849AB01}">
-  <dimension ref="A1:Y37"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:Y48"/>
+  <sheetFormatPr defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.7"/>
   <cols>
-    <col min="1" max="1" width="24.19921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.1875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.5" customWidth="1"/>
-    <col min="3" max="3" width="9.8984375" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" customWidth="1"/>
+    <col min="3" max="3" width="9.875" customWidth="1"/>
+    <col min="4" max="4" width="9.625" customWidth="1"/>
     <col min="5" max="5" width="15.5" customWidth="1"/>
     <col min="6" max="6" width="9" customWidth="1"/>
     <col min="7" max="7" width="10.5" customWidth="1"/>
     <col min="8" max="8" width="17.5" customWidth="1"/>
     <col min="9" max="9" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.8984375" customWidth="1"/>
-    <col min="11" max="11" width="17.19921875" customWidth="1"/>
-    <col min="12" max="12" width="17.3984375" customWidth="1"/>
-    <col min="13" max="13" width="16.8984375" customWidth="1"/>
-    <col min="14" max="14" width="18.19921875" customWidth="1"/>
-    <col min="15" max="15" width="25.3984375" customWidth="1"/>
-    <col min="16" max="17" width="24.69921875" customWidth="1"/>
-    <col min="18" max="18" width="10.09765625" customWidth="1"/>
-    <col min="19" max="19" width="17.59765625" customWidth="1"/>
-    <col min="20" max="20" width="12.69921875" customWidth="1"/>
-    <col min="21" max="21" width="12.09765625" customWidth="1"/>
-    <col min="22" max="22" width="13.69921875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="15.69921875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="19.3984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.875" customWidth="1"/>
+    <col min="11" max="11" width="17.1875" customWidth="1"/>
+    <col min="12" max="12" width="17.375" customWidth="1"/>
+    <col min="13" max="13" width="16.875" customWidth="1"/>
+    <col min="14" max="14" width="18.1875" customWidth="1"/>
+    <col min="15" max="15" width="25.375" customWidth="1"/>
+    <col min="16" max="17" width="24.6875" customWidth="1"/>
+    <col min="18" max="18" width="10.125" customWidth="1"/>
+    <col min="19" max="19" width="17.625" customWidth="1"/>
+    <col min="20" max="20" width="12.6875" customWidth="1"/>
+    <col min="21" max="21" width="12.125" customWidth="1"/>
+    <col min="22" max="22" width="13.6875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="15.6875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="19.375" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="12.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2450,12 +3141,12 @@
         <v>92</v>
       </c>
       <c r="Y1" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.45">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.7">
       <c r="A2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -2524,15 +3215,15 @@
         <v>0</v>
       </c>
       <c r="X2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="Y2">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.7">
       <c r="A3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -2544,7 +3235,7 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>-25</v>
+        <v>-50</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -2601,18 +3292,18 @@
         <v>0</v>
       </c>
       <c r="X3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="Y3">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.7">
       <c r="A4" t="s">
-        <v>130</v>
+        <v>221</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -2624,7 +3315,7 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -2639,13 +3330,13 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="L4">
         <v>0</v>
       </c>
       <c r="M4">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="N4">
         <v>0</v>
@@ -2676,23 +3367,26 @@
       </c>
       <c r="W4">
         <v>0</v>
+      </c>
+      <c r="X4" t="s">
+        <v>181</v>
       </c>
       <c r="Y4">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.7">
       <c r="A5" t="s">
-        <v>131</v>
+        <v>222</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -2713,161 +3407,167 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="L5">
         <v>0</v>
       </c>
       <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5" t="b">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>1</v>
+      </c>
+      <c r="V5">
+        <v>1</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
+      <c r="X5" t="s">
+        <v>182</v>
+      </c>
+      <c r="Y5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.7">
+      <c r="A6" t="s">
+        <v>223</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>-0.2</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6" t="b">
+        <v>1</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>1</v>
+      </c>
+      <c r="V6">
+        <v>1</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="X6" t="s">
+        <v>183</v>
+      </c>
+      <c r="Y6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.7">
+      <c r="A7" t="s">
+        <v>129</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
         <v>0.15</v>
       </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
-      <c r="P5">
-        <v>0</v>
-      </c>
-      <c r="Q5">
-        <v>0</v>
-      </c>
-      <c r="R5" t="b">
-        <v>0</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>1</v>
-      </c>
-      <c r="V5">
-        <v>1</v>
-      </c>
-      <c r="W5">
-        <v>0</v>
-      </c>
-      <c r="Y5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>132</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>0.3</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <v>0.2</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="P6">
-        <v>0</v>
-      </c>
-      <c r="Q6">
-        <v>0</v>
-      </c>
-      <c r="R6" t="b">
-        <v>0</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>1</v>
-      </c>
-      <c r="V6">
-        <v>1</v>
-      </c>
-      <c r="W6">
-        <v>0</v>
-      </c>
-      <c r="Y6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>158</v>
-      </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
       <c r="L7">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="N7">
         <v>0</v>
@@ -2885,7 +3585,7 @@
         <v>0</v>
       </c>
       <c r="S7">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -2903,2211 +3603,3040 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.7">
       <c r="A8" t="s">
+        <v>206</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0.2</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0.15</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8" t="b">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>1</v>
+      </c>
+      <c r="V8">
+        <v>4</v>
+      </c>
+      <c r="W8">
+        <v>1</v>
+      </c>
+      <c r="Y8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.7">
+      <c r="A9" t="s">
+        <v>130</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0.3</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0.2</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <v>0</v>
+      </c>
+      <c r="R9" t="b">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>1</v>
+      </c>
+      <c r="V9">
+        <v>1</v>
+      </c>
+      <c r="W9">
+        <v>0</v>
+      </c>
+      <c r="Y9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.7">
+      <c r="A10" t="s">
+        <v>156</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>0.15</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <v>0</v>
+      </c>
+      <c r="R10" t="b">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0.1</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>1</v>
+      </c>
+      <c r="V10">
+        <v>1</v>
+      </c>
+      <c r="W10">
+        <v>0</v>
+      </c>
+      <c r="Y10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.7">
+      <c r="A11" t="s">
+        <v>208</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0.2</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11">
+        <v>0</v>
+      </c>
+      <c r="R11" t="b">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>0.15</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>1</v>
+      </c>
+      <c r="V11">
+        <v>1</v>
+      </c>
+      <c r="W11">
+        <v>0</v>
+      </c>
+      <c r="Y11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.7">
+      <c r="A12" t="s">
+        <v>157</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0.3</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <v>0</v>
+      </c>
+      <c r="R12" t="b">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0.2</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>1</v>
+      </c>
+      <c r="V12">
+        <v>1</v>
+      </c>
+      <c r="W12">
+        <v>0</v>
+      </c>
+      <c r="Y12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.7">
+      <c r="A13" t="s">
+        <v>207</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0.3</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0.2</v>
+      </c>
+      <c r="G13">
+        <v>0.2</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>-0.2</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>0.3</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13" t="b">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>1</v>
+      </c>
+      <c r="V13">
+        <v>1</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="Y13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.7">
+      <c r="A14" t="s">
+        <v>209</v>
+      </c>
+      <c r="B14">
+        <v>0.3</v>
+      </c>
+      <c r="C14">
+        <v>0.2</v>
+      </c>
+      <c r="D14">
+        <v>-0.2</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0.2</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>0.3</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="R14" t="b">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0.3</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>1</v>
+      </c>
+      <c r="V14">
+        <v>7</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="Y14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.7">
+      <c r="A15" t="s">
+        <v>82</v>
+      </c>
+      <c r="B15">
+        <v>0.2</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>-0.2</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <v>0</v>
+      </c>
+      <c r="R15" t="b">
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>1</v>
+      </c>
+      <c r="V15">
+        <v>1</v>
+      </c>
+      <c r="W15">
+        <v>0</v>
+      </c>
+      <c r="Y15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.7">
+      <c r="A16" t="s">
+        <v>83</v>
+      </c>
+      <c r="B16">
+        <v>-0.2</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0.2</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>0</v>
+      </c>
+      <c r="Q16">
+        <v>0</v>
+      </c>
+      <c r="R16" t="b">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>1</v>
+      </c>
+      <c r="V16">
+        <v>1</v>
+      </c>
+      <c r="W16">
+        <v>0</v>
+      </c>
+      <c r="Y16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.7">
+      <c r="A17" t="s">
+        <v>134</v>
+      </c>
+      <c r="B17">
+        <v>0</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>0</v>
+      </c>
+      <c r="Q17">
+        <v>0</v>
+      </c>
+      <c r="R17" t="b">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>0.1</v>
+      </c>
+      <c r="T17">
+        <v>1</v>
+      </c>
+      <c r="U17">
+        <v>1</v>
+      </c>
+      <c r="V17">
+        <v>1</v>
+      </c>
+      <c r="W17">
+        <v>0</v>
+      </c>
+      <c r="Y17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.7">
+      <c r="A18" t="s">
+        <v>135</v>
+      </c>
+      <c r="B18">
+        <v>0.1</v>
+      </c>
+      <c r="C18">
+        <v>0.1</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>0</v>
+      </c>
+      <c r="Q18">
+        <v>0</v>
+      </c>
+      <c r="R18" t="b">
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
+      <c r="U18">
+        <v>1</v>
+      </c>
+      <c r="V18">
+        <v>1</v>
+      </c>
+      <c r="W18">
+        <v>0</v>
+      </c>
+      <c r="Y18">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.7">
+      <c r="A19" t="s">
+        <v>98</v>
+      </c>
+      <c r="B19">
+        <v>0</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0.15</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>0</v>
+      </c>
+      <c r="R19" t="b">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <v>1</v>
+      </c>
+      <c r="V19">
+        <v>1</v>
+      </c>
+      <c r="W19">
+        <v>0</v>
+      </c>
+      <c r="Y19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25" x14ac:dyDescent="0.7">
+      <c r="A20" t="s">
+        <v>105</v>
+      </c>
+      <c r="B20">
+        <v>0.15</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>0</v>
+      </c>
+      <c r="R20" t="b">
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>0</v>
+      </c>
+      <c r="U20">
+        <v>1</v>
+      </c>
+      <c r="V20">
+        <v>1</v>
+      </c>
+      <c r="W20">
+        <v>0</v>
+      </c>
+      <c r="Y20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.7">
+      <c r="A21" t="s">
+        <v>108</v>
+      </c>
+      <c r="B21">
+        <v>0</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0.15</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <v>0</v>
+      </c>
+      <c r="R21" t="b">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <v>1</v>
+      </c>
+      <c r="V21">
+        <v>1</v>
+      </c>
+      <c r="W21">
+        <v>0</v>
+      </c>
+      <c r="Y21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.7">
+      <c r="A22" t="s">
+        <v>115</v>
+      </c>
+      <c r="B22">
+        <v>0.15</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <v>0</v>
+      </c>
+      <c r="R22" t="b">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>1</v>
+      </c>
+      <c r="V22">
+        <v>1</v>
+      </c>
+      <c r="W22">
+        <v>0</v>
+      </c>
+      <c r="Y22">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25" x14ac:dyDescent="0.7">
+      <c r="A23" t="s">
+        <v>120</v>
+      </c>
+      <c r="B23">
+        <v>0.2</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="Q23">
+        <v>0</v>
+      </c>
+      <c r="R23" t="b">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>1</v>
+      </c>
+      <c r="V23">
+        <v>3</v>
+      </c>
+      <c r="W23">
+        <v>1</v>
+      </c>
+      <c r="Y23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25" x14ac:dyDescent="0.7">
+      <c r="A24" t="s">
+        <v>116</v>
+      </c>
+      <c r="B24">
+        <v>0.1</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>0</v>
+      </c>
+      <c r="Q24">
+        <v>0</v>
+      </c>
+      <c r="R24" t="b">
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
+      <c r="U24">
+        <v>1</v>
+      </c>
+      <c r="V24">
+        <v>1</v>
+      </c>
+      <c r="W24">
+        <v>0</v>
+      </c>
+      <c r="Y24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25" x14ac:dyDescent="0.7">
+      <c r="A25" t="s">
+        <v>121</v>
+      </c>
+      <c r="B25">
+        <v>-0.3</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <v>0</v>
+      </c>
+      <c r="Q25">
+        <v>0</v>
+      </c>
+      <c r="R25" t="b">
+        <v>0</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <v>0</v>
+      </c>
+      <c r="U25">
+        <v>3</v>
+      </c>
+      <c r="V25">
+        <v>1</v>
+      </c>
+      <c r="W25">
+        <v>0</v>
+      </c>
+      <c r="Y25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25" x14ac:dyDescent="0.7">
+      <c r="A26" t="s">
+        <v>117</v>
+      </c>
+      <c r="B26">
+        <v>0</v>
+      </c>
+      <c r="C26">
+        <v>0.15</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="P26">
+        <v>0</v>
+      </c>
+      <c r="Q26">
+        <v>0</v>
+      </c>
+      <c r="R26" t="b">
+        <v>0</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <v>0</v>
+      </c>
+      <c r="U26">
+        <v>1</v>
+      </c>
+      <c r="V26">
+        <v>1</v>
+      </c>
+      <c r="W26">
+        <v>0</v>
+      </c>
+      <c r="Y26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25" x14ac:dyDescent="0.7">
+      <c r="A27" t="s">
         <v>159</v>
       </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="L8">
+      <c r="B27">
+        <v>0.15</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+      <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27">
+        <v>0</v>
+      </c>
+      <c r="Q27">
+        <v>0</v>
+      </c>
+      <c r="R27" t="b">
+        <v>0</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+      <c r="T27">
+        <v>0</v>
+      </c>
+      <c r="U27">
+        <v>1</v>
+      </c>
+      <c r="V27">
+        <v>1</v>
+      </c>
+      <c r="W27">
+        <v>0</v>
+      </c>
+      <c r="Y27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25" x14ac:dyDescent="0.7">
+      <c r="A28" t="s">
+        <v>160</v>
+      </c>
+      <c r="B28">
+        <v>0</v>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
         <v>0.2</v>
       </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8">
-        <v>0</v>
-      </c>
-      <c r="P8">
-        <v>0</v>
-      </c>
-      <c r="Q8">
-        <v>0</v>
-      </c>
-      <c r="R8" t="b">
-        <v>0</v>
-      </c>
-      <c r="S8">
+      <c r="G28">
         <v>0.15</v>
       </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>1</v>
-      </c>
-      <c r="V8">
-        <v>1</v>
-      </c>
-      <c r="W8">
-        <v>0</v>
-      </c>
-      <c r="Y8">
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <v>0</v>
+      </c>
+      <c r="Q28">
+        <v>0</v>
+      </c>
+      <c r="R28" t="b">
+        <v>0</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <v>0</v>
+      </c>
+      <c r="U28">
+        <v>1</v>
+      </c>
+      <c r="V28">
+        <v>1</v>
+      </c>
+      <c r="W28">
+        <v>0</v>
+      </c>
+      <c r="X28" t="s">
+        <v>109</v>
+      </c>
+      <c r="Y28">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>160</v>
-      </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <v>0</v>
-      </c>
-      <c r="L9">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.7">
+      <c r="A29" t="s">
+        <v>162</v>
+      </c>
+      <c r="B29">
+        <v>-0.3</v>
+      </c>
+      <c r="C29">
+        <v>0</v>
+      </c>
+      <c r="D29">
+        <v>0</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29">
+        <v>0</v>
+      </c>
+      <c r="Q29">
+        <v>0</v>
+      </c>
+      <c r="R29" t="b">
+        <v>0</v>
+      </c>
+      <c r="S29">
+        <v>0</v>
+      </c>
+      <c r="T29">
+        <v>0</v>
+      </c>
+      <c r="U29">
+        <v>1</v>
+      </c>
+      <c r="V29">
+        <v>5</v>
+      </c>
+      <c r="W29">
+        <v>0</v>
+      </c>
+      <c r="Y29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25" x14ac:dyDescent="0.7">
+      <c r="A30" t="s">
+        <v>163</v>
+      </c>
+      <c r="B30">
+        <v>0</v>
+      </c>
+      <c r="C30">
+        <v>0</v>
+      </c>
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <v>0.15</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>0</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30">
+        <v>0</v>
+      </c>
+      <c r="N30">
+        <v>0</v>
+      </c>
+      <c r="O30">
+        <v>0</v>
+      </c>
+      <c r="P30">
+        <v>0</v>
+      </c>
+      <c r="Q30">
+        <v>0</v>
+      </c>
+      <c r="R30" t="b">
+        <v>0</v>
+      </c>
+      <c r="S30">
+        <v>0</v>
+      </c>
+      <c r="T30">
+        <v>0</v>
+      </c>
+      <c r="U30">
+        <v>1</v>
+      </c>
+      <c r="V30">
+        <v>1</v>
+      </c>
+      <c r="W30">
+        <v>0</v>
+      </c>
+      <c r="X30" t="s">
+        <v>109</v>
+      </c>
+      <c r="Y30">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25" x14ac:dyDescent="0.7">
+      <c r="A31" t="s">
+        <v>165</v>
+      </c>
+      <c r="B31">
         <v>0.3</v>
       </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9">
-        <v>0</v>
-      </c>
-      <c r="P9">
-        <v>0</v>
-      </c>
-      <c r="Q9">
-        <v>0</v>
-      </c>
-      <c r="R9" t="b">
-        <v>0</v>
-      </c>
-      <c r="S9">
+      <c r="C31">
+        <v>0</v>
+      </c>
+      <c r="D31">
+        <v>0</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>0</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31">
+        <v>0</v>
+      </c>
+      <c r="N31">
+        <v>0</v>
+      </c>
+      <c r="O31">
+        <v>0</v>
+      </c>
+      <c r="P31">
+        <v>0</v>
+      </c>
+      <c r="Q31">
+        <v>0</v>
+      </c>
+      <c r="R31" t="b">
+        <v>0</v>
+      </c>
+      <c r="S31">
+        <v>0</v>
+      </c>
+      <c r="T31">
+        <v>0</v>
+      </c>
+      <c r="U31">
+        <v>3</v>
+      </c>
+      <c r="V31">
+        <v>1</v>
+      </c>
+      <c r="W31">
+        <v>0</v>
+      </c>
+      <c r="Y31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25" x14ac:dyDescent="0.7">
+      <c r="A32" t="s">
+        <v>166</v>
+      </c>
+      <c r="B32">
+        <v>0</v>
+      </c>
+      <c r="C32">
         <v>0.2</v>
       </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
-      <c r="U9">
-        <v>1</v>
-      </c>
-      <c r="V9">
-        <v>1</v>
-      </c>
-      <c r="W9">
-        <v>0</v>
-      </c>
-      <c r="Y9">
+      <c r="D32">
+        <v>0</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32">
+        <v>0.1</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>0</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32">
+        <v>0</v>
+      </c>
+      <c r="P32">
+        <v>0</v>
+      </c>
+      <c r="Q32">
+        <v>0</v>
+      </c>
+      <c r="R32" t="b">
+        <v>0</v>
+      </c>
+      <c r="S32">
+        <v>0</v>
+      </c>
+      <c r="T32">
+        <v>0</v>
+      </c>
+      <c r="U32">
+        <v>1</v>
+      </c>
+      <c r="V32">
+        <v>1</v>
+      </c>
+      <c r="W32">
+        <v>0</v>
+      </c>
+      <c r="Y32">
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>82</v>
-      </c>
-      <c r="B10">
+    <row r="33" spans="1:25" x14ac:dyDescent="0.7">
+      <c r="A33" t="s">
+        <v>211</v>
+      </c>
+      <c r="B33">
         <v>0.2</v>
       </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
+      <c r="C33">
+        <v>0</v>
+      </c>
+      <c r="D33">
+        <v>0</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>0</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33">
+        <v>0</v>
+      </c>
+      <c r="O33">
+        <v>0</v>
+      </c>
+      <c r="P33">
+        <v>0</v>
+      </c>
+      <c r="Q33">
+        <v>0</v>
+      </c>
+      <c r="R33" t="b">
+        <v>0</v>
+      </c>
+      <c r="S33">
+        <v>0</v>
+      </c>
+      <c r="T33">
+        <v>0</v>
+      </c>
+      <c r="U33">
+        <v>1</v>
+      </c>
+      <c r="V33">
+        <v>3</v>
+      </c>
+      <c r="W33">
+        <v>1</v>
+      </c>
+      <c r="Y33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:25" x14ac:dyDescent="0.7">
+      <c r="A34" t="s">
+        <v>212</v>
+      </c>
+      <c r="B34">
+        <v>0</v>
+      </c>
+      <c r="C34">
+        <v>0</v>
+      </c>
+      <c r="D34">
+        <v>0.3</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>0</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+      <c r="N34">
+        <v>0</v>
+      </c>
+      <c r="O34">
+        <v>0</v>
+      </c>
+      <c r="P34">
+        <v>0</v>
+      </c>
+      <c r="Q34">
+        <v>0</v>
+      </c>
+      <c r="R34" t="b">
+        <v>0</v>
+      </c>
+      <c r="S34">
+        <v>0</v>
+      </c>
+      <c r="T34">
+        <v>0</v>
+      </c>
+      <c r="U34">
+        <v>1</v>
+      </c>
+      <c r="V34">
+        <v>1</v>
+      </c>
+      <c r="W34">
+        <v>0</v>
+      </c>
+      <c r="Y34">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:25" x14ac:dyDescent="0.7">
+      <c r="A35" t="s">
+        <v>213</v>
+      </c>
+      <c r="B35">
+        <v>-0.3</v>
+      </c>
+      <c r="C35">
+        <v>0</v>
+      </c>
+      <c r="D35">
+        <v>0</v>
+      </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
+      <c r="F35">
+        <v>0</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>0</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35">
+        <v>0</v>
+      </c>
+      <c r="N35">
+        <v>0</v>
+      </c>
+      <c r="O35">
+        <v>0</v>
+      </c>
+      <c r="P35">
+        <v>0</v>
+      </c>
+      <c r="Q35">
+        <v>0</v>
+      </c>
+      <c r="R35" t="b">
+        <v>0</v>
+      </c>
+      <c r="S35">
+        <v>0</v>
+      </c>
+      <c r="T35">
+        <v>0</v>
+      </c>
+      <c r="U35">
+        <v>1</v>
+      </c>
+      <c r="V35">
+        <v>5</v>
+      </c>
+      <c r="W35">
+        <v>0</v>
+      </c>
+      <c r="Y35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:25" x14ac:dyDescent="0.7">
+      <c r="A36" t="s">
+        <v>214</v>
+      </c>
+      <c r="B36">
+        <v>0</v>
+      </c>
+      <c r="C36">
+        <v>0</v>
+      </c>
+      <c r="D36">
+        <v>0</v>
+      </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
+      <c r="F36">
+        <v>0</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>0</v>
+      </c>
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36">
+        <v>0</v>
+      </c>
+      <c r="N36">
+        <v>0</v>
+      </c>
+      <c r="O36">
+        <v>0</v>
+      </c>
+      <c r="P36">
+        <v>0</v>
+      </c>
+      <c r="Q36">
+        <v>0</v>
+      </c>
+      <c r="R36" t="b">
+        <v>0</v>
+      </c>
+      <c r="S36">
+        <v>0.1</v>
+      </c>
+      <c r="T36">
+        <v>0</v>
+      </c>
+      <c r="U36">
+        <v>1</v>
+      </c>
+      <c r="V36">
+        <v>7</v>
+      </c>
+      <c r="W36">
+        <v>0</v>
+      </c>
+      <c r="Y36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:25" x14ac:dyDescent="0.7">
+      <c r="A37" t="s">
+        <v>215</v>
+      </c>
+      <c r="B37">
+        <v>0.3</v>
+      </c>
+      <c r="C37">
+        <v>0</v>
+      </c>
+      <c r="D37">
+        <v>0</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
+      <c r="F37">
+        <v>0</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37">
+        <v>0</v>
+      </c>
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37">
+        <v>0</v>
+      </c>
+      <c r="N37">
+        <v>0</v>
+      </c>
+      <c r="O37">
+        <v>0</v>
+      </c>
+      <c r="P37">
+        <v>0</v>
+      </c>
+      <c r="Q37">
+        <v>0</v>
+      </c>
+      <c r="R37" t="b">
+        <v>0</v>
+      </c>
+      <c r="S37">
+        <v>0</v>
+      </c>
+      <c r="T37">
+        <v>0</v>
+      </c>
+      <c r="U37">
+        <v>1</v>
+      </c>
+      <c r="V37">
+        <v>1</v>
+      </c>
+      <c r="W37">
+        <v>0</v>
+      </c>
+      <c r="Y37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:25" x14ac:dyDescent="0.7">
+      <c r="A38" t="s">
+        <v>216</v>
+      </c>
+      <c r="B38">
+        <v>0</v>
+      </c>
+      <c r="C38">
+        <v>0</v>
+      </c>
+      <c r="D38">
+        <v>0</v>
+      </c>
+      <c r="E38">
+        <v>0</v>
+      </c>
+      <c r="F38">
+        <v>0.1</v>
+      </c>
+      <c r="G38">
+        <v>0.1</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>0</v>
+      </c>
+      <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="M38">
+        <v>0</v>
+      </c>
+      <c r="N38">
+        <v>0</v>
+      </c>
+      <c r="O38">
+        <v>0</v>
+      </c>
+      <c r="P38">
+        <v>0</v>
+      </c>
+      <c r="Q38">
+        <v>0</v>
+      </c>
+      <c r="R38" t="b">
+        <v>0</v>
+      </c>
+      <c r="S38">
+        <v>0</v>
+      </c>
+      <c r="T38">
+        <v>0</v>
+      </c>
+      <c r="U38">
+        <v>1</v>
+      </c>
+      <c r="V38">
+        <v>1</v>
+      </c>
+      <c r="W38">
+        <v>0</v>
+      </c>
+      <c r="Y38">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:25" x14ac:dyDescent="0.7">
+      <c r="A39" t="s">
+        <v>217</v>
+      </c>
+      <c r="B39">
+        <v>0.3</v>
+      </c>
+      <c r="C39">
+        <v>0</v>
+      </c>
+      <c r="D39">
+        <v>0</v>
+      </c>
+      <c r="E39">
+        <v>0</v>
+      </c>
+      <c r="F39">
+        <v>0</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <v>0</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <v>0</v>
+      </c>
+      <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="M39">
+        <v>0</v>
+      </c>
+      <c r="N39">
+        <v>0</v>
+      </c>
+      <c r="O39">
+        <v>0</v>
+      </c>
+      <c r="P39">
+        <v>0</v>
+      </c>
+      <c r="Q39">
+        <v>0</v>
+      </c>
+      <c r="R39" t="b">
+        <v>0</v>
+      </c>
+      <c r="S39">
+        <v>0</v>
+      </c>
+      <c r="T39">
+        <v>0</v>
+      </c>
+      <c r="U39">
+        <v>1</v>
+      </c>
+      <c r="V39">
+        <v>3</v>
+      </c>
+      <c r="W39">
+        <v>2</v>
+      </c>
+      <c r="Y39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:25" x14ac:dyDescent="0.7">
+      <c r="A40" t="s">
+        <v>218</v>
+      </c>
+      <c r="B40">
+        <v>0</v>
+      </c>
+      <c r="C40">
+        <v>0.1</v>
+      </c>
+      <c r="D40">
+        <v>0</v>
+      </c>
+      <c r="E40">
+        <v>0</v>
+      </c>
+      <c r="F40">
+        <v>0</v>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <v>0</v>
+      </c>
+      <c r="I40">
+        <v>0.1</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <v>0</v>
+      </c>
+      <c r="L40">
+        <v>0</v>
+      </c>
+      <c r="M40">
+        <v>0</v>
+      </c>
+      <c r="N40">
+        <v>0</v>
+      </c>
+      <c r="O40">
+        <v>0</v>
+      </c>
+      <c r="P40">
+        <v>0</v>
+      </c>
+      <c r="Q40">
+        <v>0</v>
+      </c>
+      <c r="R40" t="b">
+        <v>0</v>
+      </c>
+      <c r="S40">
+        <v>0</v>
+      </c>
+      <c r="T40">
+        <v>0</v>
+      </c>
+      <c r="U40">
+        <v>1</v>
+      </c>
+      <c r="V40">
+        <v>1</v>
+      </c>
+      <c r="W40">
+        <v>0</v>
+      </c>
+      <c r="Y40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:25" x14ac:dyDescent="0.7">
+      <c r="A41" t="s">
+        <v>219</v>
+      </c>
+      <c r="B41">
         <v>-0.2</v>
       </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <v>0</v>
-      </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
-      <c r="O10">
-        <v>0</v>
-      </c>
-      <c r="P10">
-        <v>0</v>
-      </c>
-      <c r="Q10">
-        <v>0</v>
-      </c>
-      <c r="R10" t="b">
-        <v>0</v>
-      </c>
-      <c r="S10">
-        <v>0</v>
-      </c>
-      <c r="T10">
-        <v>0</v>
-      </c>
-      <c r="U10">
-        <v>1</v>
-      </c>
-      <c r="V10">
-        <v>1</v>
-      </c>
-      <c r="W10">
-        <v>0</v>
-      </c>
-      <c r="Y10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>83</v>
-      </c>
-      <c r="B11">
+      <c r="C41">
+        <v>0</v>
+      </c>
+      <c r="D41">
+        <v>0</v>
+      </c>
+      <c r="E41">
+        <v>0</v>
+      </c>
+      <c r="F41">
+        <v>0</v>
+      </c>
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41">
+        <v>0</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41">
+        <v>0</v>
+      </c>
+      <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41">
+        <v>0</v>
+      </c>
+      <c r="N41">
+        <v>0</v>
+      </c>
+      <c r="O41">
+        <v>0</v>
+      </c>
+      <c r="P41">
+        <v>0</v>
+      </c>
+      <c r="Q41">
+        <v>0</v>
+      </c>
+      <c r="R41" t="b">
+        <v>0</v>
+      </c>
+      <c r="S41">
+        <v>0</v>
+      </c>
+      <c r="T41">
+        <v>0</v>
+      </c>
+      <c r="U41">
+        <v>1</v>
+      </c>
+      <c r="V41">
+        <v>4</v>
+      </c>
+      <c r="W41">
+        <v>1</v>
+      </c>
+      <c r="X41" t="s">
+        <v>181</v>
+      </c>
+      <c r="Y41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:25" x14ac:dyDescent="0.7">
+      <c r="A42" t="s">
+        <v>220</v>
+      </c>
+      <c r="B42">
+        <v>0</v>
+      </c>
+      <c r="C42">
+        <v>0.2</v>
+      </c>
+      <c r="D42">
+        <v>0</v>
+      </c>
+      <c r="E42">
+        <v>0</v>
+      </c>
+      <c r="F42">
+        <v>0</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+      <c r="I42">
+        <v>0.2</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42">
+        <v>0</v>
+      </c>
+      <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42">
+        <v>0</v>
+      </c>
+      <c r="N42">
+        <v>0</v>
+      </c>
+      <c r="O42">
+        <v>0</v>
+      </c>
+      <c r="P42">
+        <v>0</v>
+      </c>
+      <c r="Q42">
+        <v>0</v>
+      </c>
+      <c r="R42" t="b">
+        <v>0</v>
+      </c>
+      <c r="S42">
+        <v>0</v>
+      </c>
+      <c r="T42">
+        <v>0</v>
+      </c>
+      <c r="U42">
+        <v>1</v>
+      </c>
+      <c r="V42">
+        <v>1</v>
+      </c>
+      <c r="W42">
+        <v>0</v>
+      </c>
+      <c r="Y42">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:25" x14ac:dyDescent="0.7">
+      <c r="A43" t="s">
+        <v>123</v>
+      </c>
+      <c r="B43">
+        <v>0.2</v>
+      </c>
+      <c r="C43">
+        <v>0</v>
+      </c>
+      <c r="D43">
+        <v>0</v>
+      </c>
+      <c r="E43">
+        <v>0</v>
+      </c>
+      <c r="F43">
+        <v>0</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43">
+        <v>0</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43">
+        <v>0</v>
+      </c>
+      <c r="N43">
+        <v>0</v>
+      </c>
+      <c r="O43">
+        <v>0</v>
+      </c>
+      <c r="P43">
+        <v>0</v>
+      </c>
+      <c r="Q43">
+        <v>0</v>
+      </c>
+      <c r="R43" t="b">
+        <v>0</v>
+      </c>
+      <c r="S43">
+        <v>0</v>
+      </c>
+      <c r="T43">
+        <v>0</v>
+      </c>
+      <c r="U43">
+        <v>1</v>
+      </c>
+      <c r="V43">
+        <v>1</v>
+      </c>
+      <c r="W43">
+        <v>0</v>
+      </c>
+      <c r="Y43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:25" x14ac:dyDescent="0.7">
+      <c r="A44" t="s">
+        <v>118</v>
+      </c>
+      <c r="B44">
+        <v>0</v>
+      </c>
+      <c r="C44">
+        <v>0</v>
+      </c>
+      <c r="D44">
+        <v>0.1</v>
+      </c>
+      <c r="E44">
+        <v>0</v>
+      </c>
+      <c r="F44">
+        <v>0</v>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <v>0</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44">
+        <v>0</v>
+      </c>
+      <c r="L44">
+        <v>0</v>
+      </c>
+      <c r="M44">
+        <v>0</v>
+      </c>
+      <c r="N44">
+        <v>0</v>
+      </c>
+      <c r="O44">
+        <v>0</v>
+      </c>
+      <c r="P44">
+        <v>0</v>
+      </c>
+      <c r="Q44">
+        <v>0</v>
+      </c>
+      <c r="R44" t="b">
+        <v>0</v>
+      </c>
+      <c r="S44">
+        <v>0</v>
+      </c>
+      <c r="T44">
+        <v>0</v>
+      </c>
+      <c r="U44">
+        <v>1</v>
+      </c>
+      <c r="V44">
+        <v>1</v>
+      </c>
+      <c r="W44">
+        <v>0</v>
+      </c>
+      <c r="Y44">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:25" x14ac:dyDescent="0.7">
+      <c r="A45" t="s">
+        <v>122</v>
+      </c>
+      <c r="B45">
         <v>-0.2</v>
       </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>0.2</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
-      <c r="O11">
-        <v>0</v>
-      </c>
-      <c r="P11">
-        <v>0</v>
-      </c>
-      <c r="Q11">
-        <v>0</v>
-      </c>
-      <c r="R11" t="b">
-        <v>0</v>
-      </c>
-      <c r="S11">
-        <v>0</v>
-      </c>
-      <c r="T11">
-        <v>0</v>
-      </c>
-      <c r="U11">
-        <v>1</v>
-      </c>
-      <c r="V11">
-        <v>1</v>
-      </c>
-      <c r="W11">
-        <v>0</v>
-      </c>
-      <c r="Y11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>136</v>
-      </c>
-      <c r="B12">
-        <v>0</v>
-      </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <v>0</v>
-      </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
-      <c r="M12">
-        <v>0</v>
-      </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
-      <c r="O12">
-        <v>0</v>
-      </c>
-      <c r="P12">
-        <v>0</v>
-      </c>
-      <c r="Q12">
-        <v>0</v>
-      </c>
-      <c r="R12" t="b">
-        <v>0</v>
-      </c>
-      <c r="S12">
-        <v>0.1</v>
-      </c>
-      <c r="T12">
-        <v>1</v>
-      </c>
-      <c r="U12">
-        <v>1</v>
-      </c>
-      <c r="V12">
-        <v>1</v>
-      </c>
-      <c r="W12">
-        <v>0</v>
-      </c>
-      <c r="Y12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>137</v>
-      </c>
-      <c r="B13">
-        <v>0.1</v>
-      </c>
-      <c r="C13">
-        <v>0.1</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="M13">
-        <v>0</v>
-      </c>
-      <c r="N13">
-        <v>0</v>
-      </c>
-      <c r="O13">
-        <v>0</v>
-      </c>
-      <c r="P13">
-        <v>0</v>
-      </c>
-      <c r="Q13">
-        <v>0</v>
-      </c>
-      <c r="R13" t="b">
-        <v>0</v>
-      </c>
-      <c r="S13">
-        <v>0</v>
-      </c>
-      <c r="T13">
-        <v>0</v>
-      </c>
-      <c r="U13">
-        <v>1</v>
-      </c>
-      <c r="V13">
-        <v>1</v>
-      </c>
-      <c r="W13">
-        <v>0</v>
-      </c>
-      <c r="Y13">
+      <c r="C45">
+        <v>0</v>
+      </c>
+      <c r="D45">
+        <v>0</v>
+      </c>
+      <c r="E45">
+        <v>0</v>
+      </c>
+      <c r="F45">
+        <v>0</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>0</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45">
+        <v>0</v>
+      </c>
+      <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="M45">
+        <v>0</v>
+      </c>
+      <c r="N45">
+        <v>0</v>
+      </c>
+      <c r="O45">
+        <v>0</v>
+      </c>
+      <c r="P45">
+        <v>0</v>
+      </c>
+      <c r="Q45">
+        <v>0</v>
+      </c>
+      <c r="R45" t="b">
+        <v>0</v>
+      </c>
+      <c r="S45">
+        <v>0</v>
+      </c>
+      <c r="T45">
+        <v>0</v>
+      </c>
+      <c r="U45">
+        <v>1</v>
+      </c>
+      <c r="V45">
         <v>3</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.45">
-      <c r="A14" t="s">
-        <v>98</v>
-      </c>
-      <c r="B14">
-        <v>0</v>
-      </c>
-      <c r="C14">
-        <v>0</v>
-      </c>
-      <c r="D14">
-        <v>0</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-      <c r="F14">
-        <v>0</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
+      <c r="W45">
+        <v>1</v>
+      </c>
+      <c r="Y45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:25" x14ac:dyDescent="0.7">
+      <c r="A46" t="s">
+        <v>119</v>
+      </c>
+      <c r="B46">
+        <v>0</v>
+      </c>
+      <c r="C46">
+        <v>0</v>
+      </c>
+      <c r="D46">
         <v>0.15</v>
       </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14">
-        <v>0</v>
-      </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
-      <c r="M14">
-        <v>0</v>
-      </c>
-      <c r="N14">
-        <v>0</v>
-      </c>
-      <c r="O14">
-        <v>0</v>
-      </c>
-      <c r="P14">
-        <v>0</v>
-      </c>
-      <c r="Q14">
-        <v>0</v>
-      </c>
-      <c r="R14" t="b">
-        <v>0</v>
-      </c>
-      <c r="S14">
-        <v>0</v>
-      </c>
-      <c r="T14">
-        <v>0</v>
-      </c>
-      <c r="U14">
-        <v>1</v>
-      </c>
-      <c r="V14">
-        <v>1</v>
-      </c>
-      <c r="W14">
-        <v>0</v>
-      </c>
-      <c r="Y14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.45">
-      <c r="A15" t="s">
-        <v>106</v>
-      </c>
-      <c r="B15">
-        <v>0.15</v>
-      </c>
-      <c r="C15">
-        <v>0</v>
-      </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15">
-        <v>0</v>
-      </c>
-      <c r="L15">
-        <v>0</v>
-      </c>
-      <c r="M15">
-        <v>0</v>
-      </c>
-      <c r="N15">
-        <v>0</v>
-      </c>
-      <c r="O15">
-        <v>0</v>
-      </c>
-      <c r="P15">
-        <v>0</v>
-      </c>
-      <c r="Q15">
-        <v>0</v>
-      </c>
-      <c r="R15" t="b">
-        <v>0</v>
-      </c>
-      <c r="S15">
-        <v>0</v>
-      </c>
-      <c r="T15">
-        <v>0</v>
-      </c>
-      <c r="U15">
-        <v>1</v>
-      </c>
-      <c r="V15">
-        <v>1</v>
-      </c>
-      <c r="W15">
-        <v>0</v>
-      </c>
-      <c r="Y15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.45">
-      <c r="A16" t="s">
-        <v>99</v>
-      </c>
-      <c r="B16">
-        <v>0</v>
-      </c>
-      <c r="C16">
-        <v>0</v>
-      </c>
-      <c r="D16">
-        <v>0</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16">
-        <v>0.15</v>
-      </c>
-      <c r="K16">
-        <v>0</v>
-      </c>
-      <c r="L16">
-        <v>0</v>
-      </c>
-      <c r="M16">
-        <v>0</v>
-      </c>
-      <c r="N16">
-        <v>0</v>
-      </c>
-      <c r="O16">
-        <v>0</v>
-      </c>
-      <c r="P16">
-        <v>0</v>
-      </c>
-      <c r="Q16">
-        <v>0</v>
-      </c>
-      <c r="R16" t="b">
-        <v>0</v>
-      </c>
-      <c r="S16">
-        <v>0</v>
-      </c>
-      <c r="T16">
-        <v>0</v>
-      </c>
-      <c r="U16">
-        <v>1</v>
-      </c>
-      <c r="V16">
-        <v>1</v>
-      </c>
-      <c r="W16">
-        <v>0</v>
-      </c>
-      <c r="Y16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.45">
-      <c r="A17" t="s">
-        <v>116</v>
-      </c>
-      <c r="B17">
-        <v>0.15</v>
-      </c>
-      <c r="C17">
-        <v>0</v>
-      </c>
-      <c r="D17">
-        <v>0</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-      <c r="F17">
-        <v>0</v>
-      </c>
-      <c r="G17">
-        <v>0</v>
-      </c>
-      <c r="H17">
-        <v>0</v>
-      </c>
-      <c r="I17">
-        <v>0</v>
-      </c>
-      <c r="J17">
-        <v>0</v>
-      </c>
-      <c r="K17">
-        <v>0</v>
-      </c>
-      <c r="L17">
-        <v>0</v>
-      </c>
-      <c r="M17">
-        <v>0</v>
-      </c>
-      <c r="N17">
-        <v>0</v>
-      </c>
-      <c r="O17">
-        <v>0</v>
-      </c>
-      <c r="P17">
-        <v>0</v>
-      </c>
-      <c r="Q17">
-        <v>0</v>
-      </c>
-      <c r="R17" t="b">
-        <v>0</v>
-      </c>
-      <c r="S17">
-        <v>0</v>
-      </c>
-      <c r="T17">
-        <v>0</v>
-      </c>
-      <c r="U17">
-        <v>1</v>
-      </c>
-      <c r="V17">
-        <v>1</v>
-      </c>
-      <c r="W17">
-        <v>0</v>
-      </c>
-      <c r="Y17">
+      <c r="E46">
+        <v>0</v>
+      </c>
+      <c r="F46">
+        <v>0</v>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>0</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46">
+        <v>0</v>
+      </c>
+      <c r="L46">
+        <v>0</v>
+      </c>
+      <c r="M46">
+        <v>0</v>
+      </c>
+      <c r="N46">
+        <v>0</v>
+      </c>
+      <c r="O46">
+        <v>0</v>
+      </c>
+      <c r="P46">
+        <v>0</v>
+      </c>
+      <c r="Q46">
+        <v>0</v>
+      </c>
+      <c r="R46" t="b">
+        <v>0</v>
+      </c>
+      <c r="S46">
+        <v>0</v>
+      </c>
+      <c r="T46">
+        <v>0</v>
+      </c>
+      <c r="U46">
+        <v>1</v>
+      </c>
+      <c r="V46">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.45">
-      <c r="A18" t="s">
-        <v>121</v>
-      </c>
-      <c r="B18">
-        <v>0.2</v>
-      </c>
-      <c r="C18">
-        <v>0</v>
-      </c>
-      <c r="D18">
-        <v>0</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-      <c r="F18">
-        <v>0</v>
-      </c>
-      <c r="G18">
-        <v>0</v>
-      </c>
-      <c r="H18">
-        <v>0</v>
-      </c>
-      <c r="I18">
-        <v>0</v>
-      </c>
-      <c r="J18">
-        <v>0</v>
-      </c>
-      <c r="K18">
-        <v>0</v>
-      </c>
-      <c r="L18">
-        <v>0</v>
-      </c>
-      <c r="M18">
-        <v>0</v>
-      </c>
-      <c r="N18">
-        <v>0</v>
-      </c>
-      <c r="O18">
-        <v>0</v>
-      </c>
-      <c r="P18">
-        <v>0</v>
-      </c>
-      <c r="Q18">
-        <v>0</v>
-      </c>
-      <c r="R18" t="b">
-        <v>0</v>
-      </c>
-      <c r="S18">
-        <v>0</v>
-      </c>
-      <c r="T18">
-        <v>0</v>
-      </c>
-      <c r="U18">
-        <v>1</v>
-      </c>
-      <c r="V18">
-        <v>3</v>
-      </c>
-      <c r="W18">
-        <v>1</v>
-      </c>
-      <c r="Y18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.45">
-      <c r="A19" t="s">
-        <v>117</v>
-      </c>
-      <c r="B19">
-        <v>0.1</v>
-      </c>
-      <c r="C19">
-        <v>0</v>
-      </c>
-      <c r="D19">
-        <v>0</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-      <c r="F19">
-        <v>0</v>
-      </c>
-      <c r="G19">
-        <v>0</v>
-      </c>
-      <c r="H19">
-        <v>0</v>
-      </c>
-      <c r="I19">
-        <v>0</v>
-      </c>
-      <c r="J19">
-        <v>0</v>
-      </c>
-      <c r="K19">
-        <v>0</v>
-      </c>
-      <c r="L19">
-        <v>0</v>
-      </c>
-      <c r="M19">
-        <v>0</v>
-      </c>
-      <c r="N19">
-        <v>0</v>
-      </c>
-      <c r="O19">
-        <v>0</v>
-      </c>
-      <c r="P19">
-        <v>0</v>
-      </c>
-      <c r="Q19">
-        <v>0</v>
-      </c>
-      <c r="R19" t="b">
-        <v>0</v>
-      </c>
-      <c r="S19">
-        <v>0</v>
-      </c>
-      <c r="T19">
-        <v>0</v>
-      </c>
-      <c r="U19">
-        <v>1</v>
-      </c>
-      <c r="V19">
-        <v>1</v>
-      </c>
-      <c r="W19">
-        <v>0</v>
-      </c>
-      <c r="Y19">
+      <c r="W46">
+        <v>0</v>
+      </c>
+      <c r="Y46">
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.45">
-      <c r="A20" t="s">
-        <v>122</v>
-      </c>
-      <c r="B20">
-        <v>-0.3</v>
-      </c>
-      <c r="C20">
-        <v>0</v>
-      </c>
-      <c r="D20">
-        <v>0</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-      <c r="F20">
-        <v>0</v>
-      </c>
-      <c r="G20">
-        <v>0</v>
-      </c>
-      <c r="H20">
-        <v>0</v>
-      </c>
-      <c r="I20">
-        <v>0</v>
-      </c>
-      <c r="J20">
-        <v>0</v>
-      </c>
-      <c r="K20">
-        <v>0</v>
-      </c>
-      <c r="L20">
-        <v>0</v>
-      </c>
-      <c r="M20">
-        <v>0</v>
-      </c>
-      <c r="N20">
-        <v>0</v>
-      </c>
-      <c r="O20">
-        <v>0</v>
-      </c>
-      <c r="P20">
-        <v>0</v>
-      </c>
-      <c r="Q20">
-        <v>0</v>
-      </c>
-      <c r="R20" t="b">
-        <v>0</v>
-      </c>
-      <c r="S20">
-        <v>0</v>
-      </c>
-      <c r="T20">
-        <v>0</v>
-      </c>
-      <c r="U20">
-        <v>3</v>
-      </c>
-      <c r="V20">
-        <v>1</v>
-      </c>
-      <c r="W20">
-        <v>0</v>
-      </c>
-      <c r="Y20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.45">
-      <c r="A21" t="s">
-        <v>118</v>
-      </c>
-      <c r="B21">
-        <v>0</v>
-      </c>
-      <c r="C21">
-        <v>0.15</v>
-      </c>
-      <c r="D21">
-        <v>0</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-      <c r="F21">
-        <v>0</v>
-      </c>
-      <c r="G21">
-        <v>0</v>
-      </c>
-      <c r="H21">
-        <v>0</v>
-      </c>
-      <c r="I21">
-        <v>0</v>
-      </c>
-      <c r="J21">
-        <v>0</v>
-      </c>
-      <c r="K21">
-        <v>0</v>
-      </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
-      <c r="M21">
-        <v>0</v>
-      </c>
-      <c r="N21">
-        <v>0</v>
-      </c>
-      <c r="O21">
-        <v>0</v>
-      </c>
-      <c r="P21">
-        <v>0</v>
-      </c>
-      <c r="Q21">
-        <v>0</v>
-      </c>
-      <c r="R21" t="b">
-        <v>0</v>
-      </c>
-      <c r="S21">
-        <v>0</v>
-      </c>
-      <c r="T21">
-        <v>0</v>
-      </c>
-      <c r="U21">
-        <v>1</v>
-      </c>
-      <c r="V21">
-        <v>1</v>
-      </c>
-      <c r="W21">
-        <v>0</v>
-      </c>
-      <c r="Y21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.45">
-      <c r="A22" t="s">
-        <v>124</v>
-      </c>
-      <c r="B22">
-        <v>0.2</v>
-      </c>
-      <c r="C22">
-        <v>0</v>
-      </c>
-      <c r="D22">
-        <v>0</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-      <c r="F22">
-        <v>0</v>
-      </c>
-      <c r="G22">
-        <v>0</v>
-      </c>
-      <c r="H22">
-        <v>0</v>
-      </c>
-      <c r="I22">
-        <v>0</v>
-      </c>
-      <c r="J22">
-        <v>0</v>
-      </c>
-      <c r="K22">
-        <v>0</v>
-      </c>
-      <c r="L22">
-        <v>0</v>
-      </c>
-      <c r="M22">
-        <v>0</v>
-      </c>
-      <c r="N22">
-        <v>0</v>
-      </c>
-      <c r="O22">
-        <v>0</v>
-      </c>
-      <c r="P22">
-        <v>0</v>
-      </c>
-      <c r="Q22">
-        <v>0</v>
-      </c>
-      <c r="R22" t="b">
-        <v>0</v>
-      </c>
-      <c r="S22">
-        <v>0</v>
-      </c>
-      <c r="T22">
-        <v>0</v>
-      </c>
-      <c r="U22">
-        <v>1</v>
-      </c>
-      <c r="V22">
-        <v>1</v>
-      </c>
-      <c r="W22">
-        <v>0</v>
-      </c>
-      <c r="Y22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.45">
-      <c r="A23" t="s">
-        <v>119</v>
-      </c>
-      <c r="B23">
-        <v>0</v>
-      </c>
-      <c r="C23">
-        <v>0</v>
-      </c>
-      <c r="D23">
-        <v>0.1</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-      <c r="F23">
-        <v>0</v>
-      </c>
-      <c r="G23">
-        <v>0</v>
-      </c>
-      <c r="H23">
-        <v>0</v>
-      </c>
-      <c r="I23">
-        <v>0</v>
-      </c>
-      <c r="J23">
-        <v>0</v>
-      </c>
-      <c r="K23">
-        <v>0</v>
-      </c>
-      <c r="L23">
-        <v>0</v>
-      </c>
-      <c r="M23">
-        <v>0</v>
-      </c>
-      <c r="N23">
-        <v>0</v>
-      </c>
-      <c r="O23">
-        <v>0</v>
-      </c>
-      <c r="P23">
-        <v>0</v>
-      </c>
-      <c r="Q23">
-        <v>0</v>
-      </c>
-      <c r="R23" t="b">
-        <v>0</v>
-      </c>
-      <c r="S23">
-        <v>0</v>
-      </c>
-      <c r="T23">
-        <v>0</v>
-      </c>
-      <c r="U23">
-        <v>1</v>
-      </c>
-      <c r="V23">
-        <v>1</v>
-      </c>
-      <c r="W23">
-        <v>0</v>
-      </c>
-      <c r="Y23">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.45">
-      <c r="A24" t="s">
-        <v>123</v>
-      </c>
-      <c r="B24">
-        <v>-0.2</v>
-      </c>
-      <c r="C24">
-        <v>0</v>
-      </c>
-      <c r="D24">
-        <v>0</v>
-      </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
-      <c r="F24">
-        <v>0</v>
-      </c>
-      <c r="G24">
-        <v>0</v>
-      </c>
-      <c r="H24">
-        <v>0</v>
-      </c>
-      <c r="I24">
-        <v>0</v>
-      </c>
-      <c r="J24">
-        <v>0</v>
-      </c>
-      <c r="K24">
-        <v>0</v>
-      </c>
-      <c r="L24">
-        <v>0</v>
-      </c>
-      <c r="M24">
-        <v>0</v>
-      </c>
-      <c r="N24">
-        <v>0</v>
-      </c>
-      <c r="O24">
-        <v>0</v>
-      </c>
-      <c r="P24">
-        <v>0</v>
-      </c>
-      <c r="Q24">
-        <v>0</v>
-      </c>
-      <c r="R24" t="b">
-        <v>0</v>
-      </c>
-      <c r="S24">
-        <v>0</v>
-      </c>
-      <c r="T24">
-        <v>0</v>
-      </c>
-      <c r="U24">
-        <v>1</v>
-      </c>
-      <c r="V24">
-        <v>3</v>
-      </c>
-      <c r="W24">
-        <v>1</v>
-      </c>
-      <c r="Y24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.45">
-      <c r="A25" t="s">
-        <v>120</v>
-      </c>
-      <c r="B25">
-        <v>0</v>
-      </c>
-      <c r="C25">
-        <v>0</v>
-      </c>
-      <c r="D25">
-        <v>0.15</v>
-      </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-      <c r="F25">
-        <v>0</v>
-      </c>
-      <c r="G25">
-        <v>0</v>
-      </c>
-      <c r="H25">
-        <v>0</v>
-      </c>
-      <c r="I25">
-        <v>0</v>
-      </c>
-      <c r="J25">
-        <v>0</v>
-      </c>
-      <c r="K25">
-        <v>0</v>
-      </c>
-      <c r="L25">
-        <v>0</v>
-      </c>
-      <c r="M25">
-        <v>0</v>
-      </c>
-      <c r="N25">
-        <v>0</v>
-      </c>
-      <c r="O25">
-        <v>0</v>
-      </c>
-      <c r="P25">
-        <v>0</v>
-      </c>
-      <c r="Q25">
-        <v>0</v>
-      </c>
-      <c r="R25" t="b">
-        <v>0</v>
-      </c>
-      <c r="S25">
-        <v>0</v>
-      </c>
-      <c r="T25">
-        <v>0</v>
-      </c>
-      <c r="U25">
-        <v>1</v>
-      </c>
-      <c r="V25">
-        <v>3</v>
-      </c>
-      <c r="W25">
-        <v>0</v>
-      </c>
-      <c r="Y25">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.45">
-      <c r="A26" t="s">
-        <v>162</v>
-      </c>
-      <c r="B26">
-        <v>0.15</v>
-      </c>
-      <c r="C26">
-        <v>0</v>
-      </c>
-      <c r="D26">
-        <v>0</v>
-      </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-      <c r="F26">
-        <v>0</v>
-      </c>
-      <c r="G26">
-        <v>0</v>
-      </c>
-      <c r="H26">
-        <v>0</v>
-      </c>
-      <c r="I26">
-        <v>0</v>
-      </c>
-      <c r="J26">
-        <v>0</v>
-      </c>
-      <c r="K26">
-        <v>0</v>
-      </c>
-      <c r="L26">
-        <v>0</v>
-      </c>
-      <c r="M26">
-        <v>0</v>
-      </c>
-      <c r="N26">
-        <v>0</v>
-      </c>
-      <c r="O26">
-        <v>0</v>
-      </c>
-      <c r="P26">
-        <v>0</v>
-      </c>
-      <c r="Q26">
-        <v>0</v>
-      </c>
-      <c r="R26" t="b">
-        <v>0</v>
-      </c>
-      <c r="S26">
-        <v>0</v>
-      </c>
-      <c r="T26">
-        <v>0</v>
-      </c>
-      <c r="U26">
-        <v>1</v>
-      </c>
-      <c r="V26">
-        <v>1</v>
-      </c>
-      <c r="W26">
-        <v>0</v>
-      </c>
-      <c r="Y26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.45">
-      <c r="A27" t="s">
-        <v>163</v>
-      </c>
-      <c r="B27">
-        <v>0</v>
-      </c>
-      <c r="C27">
-        <v>0</v>
-      </c>
-      <c r="D27">
-        <v>0</v>
-      </c>
-      <c r="E27">
-        <v>0</v>
-      </c>
-      <c r="F27">
-        <v>0.2</v>
-      </c>
-      <c r="G27">
-        <v>0.15</v>
-      </c>
-      <c r="H27">
-        <v>0</v>
-      </c>
-      <c r="I27">
-        <v>0</v>
-      </c>
-      <c r="J27">
-        <v>0</v>
-      </c>
-      <c r="K27">
-        <v>0</v>
-      </c>
-      <c r="L27">
-        <v>0</v>
-      </c>
-      <c r="M27">
-        <v>0</v>
-      </c>
-      <c r="N27">
-        <v>0</v>
-      </c>
-      <c r="O27">
-        <v>0</v>
-      </c>
-      <c r="P27">
-        <v>0</v>
-      </c>
-      <c r="Q27">
-        <v>0</v>
-      </c>
-      <c r="R27" t="b">
-        <v>0</v>
-      </c>
-      <c r="S27">
-        <v>0</v>
-      </c>
-      <c r="T27">
-        <v>0</v>
-      </c>
-      <c r="U27">
-        <v>1</v>
-      </c>
-      <c r="V27">
-        <v>1</v>
-      </c>
-      <c r="W27">
-        <v>0</v>
-      </c>
-      <c r="X27" t="s">
-        <v>110</v>
-      </c>
-      <c r="Y27">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.45">
-      <c r="A28" t="s">
-        <v>165</v>
-      </c>
-      <c r="B28">
-        <v>-0.3</v>
-      </c>
-      <c r="C28">
-        <v>0</v>
-      </c>
-      <c r="D28">
-        <v>0</v>
-      </c>
-      <c r="E28">
-        <v>0</v>
-      </c>
-      <c r="F28">
-        <v>0</v>
-      </c>
-      <c r="G28">
-        <v>0</v>
-      </c>
-      <c r="H28">
-        <v>0</v>
-      </c>
-      <c r="I28">
-        <v>0</v>
-      </c>
-      <c r="J28">
-        <v>0</v>
-      </c>
-      <c r="K28">
-        <v>0</v>
-      </c>
-      <c r="L28">
-        <v>0</v>
-      </c>
-      <c r="M28">
-        <v>0</v>
-      </c>
-      <c r="N28">
-        <v>0</v>
-      </c>
-      <c r="O28">
-        <v>0</v>
-      </c>
-      <c r="P28">
-        <v>0</v>
-      </c>
-      <c r="Q28">
-        <v>0</v>
-      </c>
-      <c r="R28" t="b">
-        <v>0</v>
-      </c>
-      <c r="S28">
-        <v>0</v>
-      </c>
-      <c r="T28">
-        <v>0</v>
-      </c>
-      <c r="U28">
-        <v>1</v>
-      </c>
-      <c r="V28">
-        <v>5</v>
-      </c>
-      <c r="W28">
-        <v>0</v>
-      </c>
-      <c r="Y28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.45">
-      <c r="A29" t="s">
-        <v>166</v>
-      </c>
-      <c r="B29">
-        <v>0</v>
-      </c>
-      <c r="C29">
-        <v>0</v>
-      </c>
-      <c r="D29">
-        <v>0</v>
-      </c>
-      <c r="E29">
-        <v>0</v>
-      </c>
-      <c r="F29">
-        <v>0.15</v>
-      </c>
-      <c r="G29">
-        <v>0</v>
-      </c>
-      <c r="H29">
-        <v>0</v>
-      </c>
-      <c r="I29">
-        <v>0</v>
-      </c>
-      <c r="J29">
-        <v>0</v>
-      </c>
-      <c r="K29">
-        <v>0</v>
-      </c>
-      <c r="L29">
-        <v>0</v>
-      </c>
-      <c r="M29">
-        <v>0</v>
-      </c>
-      <c r="N29">
-        <v>0</v>
-      </c>
-      <c r="O29">
-        <v>0</v>
-      </c>
-      <c r="P29">
-        <v>0</v>
-      </c>
-      <c r="Q29">
-        <v>0</v>
-      </c>
-      <c r="R29" t="b">
-        <v>0</v>
-      </c>
-      <c r="S29">
-        <v>0</v>
-      </c>
-      <c r="T29">
-        <v>0</v>
-      </c>
-      <c r="U29">
-        <v>1</v>
-      </c>
-      <c r="V29">
-        <v>1</v>
-      </c>
-      <c r="W29">
-        <v>0</v>
-      </c>
-      <c r="X29" t="s">
-        <v>110</v>
-      </c>
-      <c r="Y29">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.45">
-      <c r="A30" t="s">
-        <v>168</v>
-      </c>
-      <c r="B30">
-        <v>0.3</v>
-      </c>
-      <c r="C30">
-        <v>0</v>
-      </c>
-      <c r="D30">
-        <v>0</v>
-      </c>
-      <c r="E30">
-        <v>0</v>
-      </c>
-      <c r="F30">
-        <v>0</v>
-      </c>
-      <c r="G30">
-        <v>0</v>
-      </c>
-      <c r="H30">
-        <v>0</v>
-      </c>
-      <c r="I30">
-        <v>0</v>
-      </c>
-      <c r="J30">
-        <v>0</v>
-      </c>
-      <c r="K30">
-        <v>0</v>
-      </c>
-      <c r="L30">
-        <v>0</v>
-      </c>
-      <c r="M30">
-        <v>0</v>
-      </c>
-      <c r="N30">
-        <v>0</v>
-      </c>
-      <c r="O30">
-        <v>0</v>
-      </c>
-      <c r="P30">
-        <v>0</v>
-      </c>
-      <c r="Q30">
-        <v>0</v>
-      </c>
-      <c r="R30" t="b">
-        <v>0</v>
-      </c>
-      <c r="S30">
-        <v>0</v>
-      </c>
-      <c r="T30">
-        <v>0</v>
-      </c>
-      <c r="U30">
-        <v>3</v>
-      </c>
-      <c r="V30">
-        <v>1</v>
-      </c>
-      <c r="W30">
-        <v>0</v>
-      </c>
-      <c r="Y30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.45">
-      <c r="A31" t="s">
-        <v>169</v>
-      </c>
-      <c r="B31">
-        <v>0</v>
-      </c>
-      <c r="C31">
-        <v>0.2</v>
-      </c>
-      <c r="D31">
-        <v>0</v>
-      </c>
-      <c r="E31">
-        <v>0</v>
-      </c>
-      <c r="F31">
-        <v>0.1</v>
-      </c>
-      <c r="G31">
-        <v>0</v>
-      </c>
-      <c r="H31">
-        <v>0</v>
-      </c>
-      <c r="I31">
-        <v>0</v>
-      </c>
-      <c r="J31">
-        <v>0</v>
-      </c>
-      <c r="K31">
-        <v>0</v>
-      </c>
-      <c r="L31">
-        <v>0</v>
-      </c>
-      <c r="M31">
-        <v>0</v>
-      </c>
-      <c r="N31">
-        <v>0</v>
-      </c>
-      <c r="O31">
-        <v>0</v>
-      </c>
-      <c r="P31">
-        <v>0</v>
-      </c>
-      <c r="Q31">
-        <v>0</v>
-      </c>
-      <c r="R31" t="b">
-        <v>0</v>
-      </c>
-      <c r="S31">
-        <v>0</v>
-      </c>
-      <c r="T31">
-        <v>0</v>
-      </c>
-      <c r="U31">
-        <v>1</v>
-      </c>
-      <c r="V31">
-        <v>1</v>
-      </c>
-      <c r="W31">
-        <v>0</v>
-      </c>
-      <c r="Y31">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.45">
-      <c r="B32">
-        <v>0</v>
-      </c>
-      <c r="C32">
-        <v>0</v>
-      </c>
-      <c r="D32">
-        <v>0</v>
-      </c>
-      <c r="E32">
-        <v>0</v>
-      </c>
-      <c r="F32">
-        <v>0</v>
-      </c>
-      <c r="G32">
-        <v>0</v>
-      </c>
-      <c r="H32">
-        <v>0</v>
-      </c>
-      <c r="I32">
-        <v>0</v>
-      </c>
-      <c r="J32">
-        <v>0</v>
-      </c>
-      <c r="K32">
-        <v>0</v>
-      </c>
-      <c r="L32">
-        <v>0</v>
-      </c>
-      <c r="M32">
-        <v>0</v>
-      </c>
-      <c r="N32">
-        <v>0</v>
-      </c>
-      <c r="O32">
-        <v>0</v>
-      </c>
-      <c r="P32">
-        <v>0</v>
-      </c>
-      <c r="Q32">
-        <v>0</v>
-      </c>
-      <c r="R32" t="b">
-        <v>0</v>
-      </c>
-      <c r="S32">
-        <v>0</v>
-      </c>
-      <c r="T32">
-        <v>0</v>
-      </c>
-      <c r="U32">
-        <v>1</v>
-      </c>
-      <c r="V32">
-        <v>1</v>
-      </c>
-      <c r="W32">
-        <v>0</v>
-      </c>
-      <c r="Y32">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.45">
-      <c r="B33">
-        <v>0</v>
-      </c>
-      <c r="C33">
-        <v>0</v>
-      </c>
-      <c r="D33">
-        <v>0</v>
-      </c>
-      <c r="E33">
-        <v>0</v>
-      </c>
-      <c r="F33">
-        <v>0</v>
-      </c>
-      <c r="G33">
-        <v>0</v>
-      </c>
-      <c r="H33">
-        <v>0</v>
-      </c>
-      <c r="I33">
-        <v>0</v>
-      </c>
-      <c r="J33">
-        <v>0</v>
-      </c>
-      <c r="K33">
-        <v>0</v>
-      </c>
-      <c r="L33">
-        <v>0</v>
-      </c>
-      <c r="M33">
-        <v>0</v>
-      </c>
-      <c r="N33">
-        <v>0</v>
-      </c>
-      <c r="O33">
-        <v>0</v>
-      </c>
-      <c r="P33">
-        <v>0</v>
-      </c>
-      <c r="Q33">
-        <v>0</v>
-      </c>
-      <c r="R33" t="b">
-        <v>0</v>
-      </c>
-      <c r="S33">
-        <v>0</v>
-      </c>
-      <c r="T33">
-        <v>0</v>
-      </c>
-      <c r="U33">
-        <v>1</v>
-      </c>
-      <c r="V33">
-        <v>1</v>
-      </c>
-      <c r="W33">
-        <v>0</v>
-      </c>
-      <c r="Y33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.45">
-      <c r="B34">
-        <v>0</v>
-      </c>
-      <c r="C34">
-        <v>0</v>
-      </c>
-      <c r="D34">
-        <v>0</v>
-      </c>
-      <c r="E34">
-        <v>0</v>
-      </c>
-      <c r="F34">
-        <v>0</v>
-      </c>
-      <c r="G34">
-        <v>0</v>
-      </c>
-      <c r="H34">
-        <v>0</v>
-      </c>
-      <c r="I34">
-        <v>0</v>
-      </c>
-      <c r="J34">
-        <v>0</v>
-      </c>
-      <c r="K34">
-        <v>0</v>
-      </c>
-      <c r="L34">
-        <v>0</v>
-      </c>
-      <c r="M34">
-        <v>0</v>
-      </c>
-      <c r="N34">
-        <v>0</v>
-      </c>
-      <c r="O34">
-        <v>0</v>
-      </c>
-      <c r="P34">
-        <v>0</v>
-      </c>
-      <c r="Q34">
-        <v>0</v>
-      </c>
-      <c r="R34" t="b">
-        <v>0</v>
-      </c>
-      <c r="S34">
-        <v>0</v>
-      </c>
-      <c r="T34">
-        <v>0</v>
-      </c>
-      <c r="U34">
-        <v>1</v>
-      </c>
-      <c r="V34">
-        <v>1</v>
-      </c>
-      <c r="W34">
-        <v>0</v>
-      </c>
-      <c r="Y34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.45">
-      <c r="B35">
-        <v>0</v>
-      </c>
-      <c r="C35">
-        <v>0</v>
-      </c>
-      <c r="D35">
-        <v>0</v>
-      </c>
-      <c r="E35">
-        <v>0</v>
-      </c>
-      <c r="F35">
-        <v>0</v>
-      </c>
-      <c r="G35">
-        <v>0</v>
-      </c>
-      <c r="H35">
-        <v>0</v>
-      </c>
-      <c r="I35">
-        <v>0</v>
-      </c>
-      <c r="J35">
-        <v>0</v>
-      </c>
-      <c r="K35">
-        <v>0</v>
-      </c>
-      <c r="L35">
-        <v>0</v>
-      </c>
-      <c r="M35">
-        <v>0</v>
-      </c>
-      <c r="N35">
-        <v>0</v>
-      </c>
-      <c r="O35">
-        <v>0</v>
-      </c>
-      <c r="P35">
-        <v>0</v>
-      </c>
-      <c r="Q35">
-        <v>0</v>
-      </c>
-      <c r="R35" t="b">
-        <v>0</v>
-      </c>
-      <c r="S35">
-        <v>0</v>
-      </c>
-      <c r="T35">
-        <v>0</v>
-      </c>
-      <c r="U35">
-        <v>1</v>
-      </c>
-      <c r="V35">
-        <v>1</v>
-      </c>
-      <c r="W35">
-        <v>0</v>
-      </c>
-      <c r="Y35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="2:25" x14ac:dyDescent="0.45">
-      <c r="B36">
-        <v>0</v>
-      </c>
-      <c r="C36">
-        <v>0</v>
-      </c>
-      <c r="D36">
-        <v>0</v>
-      </c>
-      <c r="E36">
-        <v>0</v>
-      </c>
-      <c r="F36">
-        <v>0</v>
-      </c>
-      <c r="G36">
-        <v>0</v>
-      </c>
-      <c r="H36">
-        <v>0</v>
-      </c>
-      <c r="I36">
-        <v>0</v>
-      </c>
-      <c r="J36">
-        <v>0</v>
-      </c>
-      <c r="K36">
-        <v>0</v>
-      </c>
-      <c r="L36">
-        <v>0</v>
-      </c>
-      <c r="M36">
-        <v>0</v>
-      </c>
-      <c r="N36">
-        <v>0</v>
-      </c>
-      <c r="O36">
-        <v>0</v>
-      </c>
-      <c r="P36">
-        <v>0</v>
-      </c>
-      <c r="Q36">
-        <v>0</v>
-      </c>
-      <c r="R36" t="b">
-        <v>0</v>
-      </c>
-      <c r="S36">
-        <v>0</v>
-      </c>
-      <c r="T36">
-        <v>0</v>
-      </c>
-      <c r="U36">
-        <v>1</v>
-      </c>
-      <c r="V36">
-        <v>1</v>
-      </c>
-      <c r="W36">
-        <v>0</v>
-      </c>
-      <c r="Y36">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.45">
-      <c r="B37">
-        <v>0</v>
-      </c>
-      <c r="C37">
-        <v>0</v>
-      </c>
-      <c r="D37">
-        <v>0</v>
-      </c>
-      <c r="E37">
-        <v>0</v>
-      </c>
-      <c r="F37">
-        <v>0</v>
-      </c>
-      <c r="G37">
-        <v>0</v>
-      </c>
-      <c r="H37">
-        <v>0</v>
-      </c>
-      <c r="I37">
-        <v>0</v>
-      </c>
-      <c r="J37">
-        <v>0</v>
-      </c>
-      <c r="K37">
-        <v>0</v>
-      </c>
-      <c r="L37">
-        <v>0</v>
-      </c>
-      <c r="M37">
-        <v>0</v>
-      </c>
-      <c r="N37">
-        <v>0</v>
-      </c>
-      <c r="O37">
-        <v>0</v>
-      </c>
-      <c r="P37">
-        <v>0</v>
-      </c>
-      <c r="Q37">
-        <v>0</v>
-      </c>
-      <c r="R37" t="b">
-        <v>0</v>
-      </c>
-      <c r="S37">
-        <v>0</v>
-      </c>
-      <c r="T37">
-        <v>0</v>
-      </c>
-      <c r="U37">
-        <v>1</v>
-      </c>
-      <c r="V37">
-        <v>1</v>
-      </c>
-      <c r="W37">
-        <v>0</v>
-      </c>
-      <c r="Y37">
+    <row r="47" spans="1:25" x14ac:dyDescent="0.7">
+      <c r="B47">
+        <v>0</v>
+      </c>
+      <c r="C47">
+        <v>0</v>
+      </c>
+      <c r="D47">
+        <v>0</v>
+      </c>
+      <c r="E47">
+        <v>0</v>
+      </c>
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>0</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47">
+        <v>0</v>
+      </c>
+      <c r="L47">
+        <v>0</v>
+      </c>
+      <c r="M47">
+        <v>0</v>
+      </c>
+      <c r="N47">
+        <v>0</v>
+      </c>
+      <c r="O47">
+        <v>0</v>
+      </c>
+      <c r="P47">
+        <v>0</v>
+      </c>
+      <c r="Q47">
+        <v>0</v>
+      </c>
+      <c r="R47" t="b">
+        <v>0</v>
+      </c>
+      <c r="S47">
+        <v>0</v>
+      </c>
+      <c r="T47">
+        <v>0</v>
+      </c>
+      <c r="U47">
+        <v>1</v>
+      </c>
+      <c r="V47">
+        <v>1</v>
+      </c>
+      <c r="W47">
+        <v>0</v>
+      </c>
+      <c r="Y47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:25" x14ac:dyDescent="0.7">
+      <c r="B48">
+        <v>0</v>
+      </c>
+      <c r="C48">
+        <v>0</v>
+      </c>
+      <c r="D48">
+        <v>0</v>
+      </c>
+      <c r="E48">
+        <v>0</v>
+      </c>
+      <c r="F48">
+        <v>0</v>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>0</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48">
+        <v>0</v>
+      </c>
+      <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48">
+        <v>0</v>
+      </c>
+      <c r="N48">
+        <v>0</v>
+      </c>
+      <c r="O48">
+        <v>0</v>
+      </c>
+      <c r="P48">
+        <v>0</v>
+      </c>
+      <c r="Q48">
+        <v>0</v>
+      </c>
+      <c r="R48" t="b">
+        <v>0</v>
+      </c>
+      <c r="S48">
+        <v>0</v>
+      </c>
+      <c r="T48">
+        <v>0</v>
+      </c>
+      <c r="U48">
+        <v>1</v>
+      </c>
+      <c r="V48">
+        <v>1</v>
+      </c>
+      <c r="W48">
+        <v>0</v>
+      </c>
+      <c r="Y48">
         <v>1</v>
       </c>
     </row>
@@ -5123,14 +6652,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECE8E980-9D75-4087-B4F8-F29B93410A36}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.7"/>
   <cols>
     <col min="1" max="1" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.69921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.5625" customWidth="1"/>
     <col min="3" max="3" width="14.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5141,31 +6670,34 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A3" t="s">
         <v>107</v>
       </c>
-      <c r="B2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
+      <c r="B3" t="s">
+        <v>180</v>
+      </c>
+      <c r="C3" t="s">
         <v>108</v>
       </c>
-      <c r="C3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A4" t="s">
         <v>97</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>178</v>
       </c>
       <c r="C4" t="s">
         <v>98</v>
@@ -5182,18 +6714,18 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{646309C0-1AC1-40CF-851B-3BE46F905216}">
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.7"/>
   <cols>
-    <col min="1" max="1" width="15.3984375" customWidth="1"/>
-    <col min="2" max="2" width="10.59765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.375" customWidth="1"/>
+    <col min="2" max="2" width="10.625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5213,9 +6745,9 @@
         <v>92</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B2">
         <v>120</v>
@@ -5230,12 +6762,12 @@
         <v>33</v>
       </c>
       <c r="F2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B3">
         <v>100</v>
@@ -5247,70 +6779,161 @@
         <v>30</v>
       </c>
       <c r="E3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A4" t="s">
-        <v>149</v>
+        <v>172</v>
       </c>
       <c r="B4">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="C4">
         <v>30</v>
       </c>
       <c r="D4">
+        <v>5</v>
+      </c>
+      <c r="E4" t="s">
+        <v>145</v>
+      </c>
+      <c r="F4" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.7">
+      <c r="A5" t="s">
+        <v>171</v>
+      </c>
+      <c r="B5">
+        <v>90</v>
+      </c>
+      <c r="C5">
+        <v>25</v>
+      </c>
+      <c r="D5">
+        <v>40</v>
+      </c>
+      <c r="E5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.7">
+      <c r="A6" t="s">
+        <v>173</v>
+      </c>
+      <c r="B6">
+        <v>130</v>
+      </c>
+      <c r="C6">
+        <v>45</v>
+      </c>
+      <c r="D6">
+        <v>10</v>
+      </c>
+      <c r="E6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.7">
+      <c r="A7" t="s">
+        <v>177</v>
+      </c>
+      <c r="B7">
+        <v>110</v>
+      </c>
+      <c r="C7">
+        <v>60</v>
+      </c>
+      <c r="D7">
+        <v>15</v>
+      </c>
+      <c r="E7" t="s">
+        <v>145</v>
+      </c>
+      <c r="F7" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.7">
+      <c r="A8" t="s">
+        <v>176</v>
+      </c>
+      <c r="B8">
+        <v>80</v>
+      </c>
+      <c r="C8">
         <v>20</v>
       </c>
-      <c r="E4" t="s">
+      <c r="D8">
+        <v>50</v>
+      </c>
+      <c r="E8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F8" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.7">
+      <c r="A9" t="s">
+        <v>147</v>
+      </c>
+      <c r="B9">
+        <v>50</v>
+      </c>
+      <c r="C9">
+        <v>30</v>
+      </c>
+      <c r="D9">
+        <v>20</v>
+      </c>
+      <c r="E9" t="s">
         <v>33</v>
       </c>
-      <c r="F4" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>150</v>
-      </c>
-      <c r="B5">
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.7">
+      <c r="A10" t="s">
+        <v>148</v>
+      </c>
+      <c r="B10">
         <v>50</v>
       </c>
-      <c r="C5">
+      <c r="C10">
         <v>30</v>
       </c>
-      <c r="D5">
+      <c r="D10">
         <v>20</v>
       </c>
-      <c r="E5" t="s">
-        <v>147</v>
-      </c>
-      <c r="F5" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>148</v>
-      </c>
-      <c r="B6">
+      <c r="E10" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.7">
+      <c r="A11" t="s">
+        <v>146</v>
+      </c>
+      <c r="B11">
         <v>50</v>
       </c>
-      <c r="C6">
+      <c r="C11">
         <v>30</v>
       </c>
-      <c r="D6">
+      <c r="D11">
         <v>20</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E11" t="s">
         <v>31</v>
-      </c>
-      <c r="F6" t="s">
-        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -5325,16 +6948,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3094CBAF-F9CC-42AA-93E3-0E10EDB827F2}">
   <dimension ref="A1:E101"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.7"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="11.8984375" customWidth="1"/>
-    <col min="3" max="3" width="12.19921875" customWidth="1"/>
-    <col min="4" max="4" width="12.59765625" customWidth="1"/>
+    <col min="2" max="2" width="11.875" customWidth="1"/>
+    <col min="3" max="3" width="12.1875" customWidth="1"/>
+    <col min="4" max="4" width="12.625" customWidth="1"/>
     <col min="5" max="5" width="23.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A1" t="s">
         <v>9</v>
       </c>
@@ -5351,7 +6974,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A2">
         <v>1</v>
       </c>
@@ -5368,7 +6991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A3">
         <v>2</v>
       </c>
@@ -5385,7 +7008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A4">
         <v>3</v>
       </c>
@@ -5402,7 +7025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A5">
         <v>4</v>
       </c>
@@ -5419,7 +7042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A6">
         <v>5</v>
       </c>
@@ -5436,7 +7059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A7">
         <v>6</v>
       </c>
@@ -5453,7 +7076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A8">
         <v>7</v>
       </c>
@@ -5470,7 +7093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A9">
         <v>8</v>
       </c>
@@ -5487,7 +7110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A10">
         <v>9</v>
       </c>
@@ -5504,7 +7127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A11">
         <v>10</v>
       </c>
@@ -5521,7 +7144,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A12">
         <v>11</v>
       </c>
@@ -5538,7 +7161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A13">
         <v>12</v>
       </c>
@@ -5555,7 +7178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A14">
         <v>13</v>
       </c>
@@ -5572,7 +7195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A15">
         <v>14</v>
       </c>
@@ -5589,7 +7212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A16">
         <v>15</v>
       </c>
@@ -5606,7 +7229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A17">
         <v>16</v>
       </c>
@@ -5623,7 +7246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A18">
         <v>17</v>
       </c>
@@ -5640,7 +7263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A19">
         <v>18</v>
       </c>
@@ -5657,7 +7280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A20">
         <v>19</v>
       </c>
@@ -5674,7 +7297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A21">
         <v>20</v>
       </c>
@@ -5691,7 +7314,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A22">
         <v>21</v>
       </c>
@@ -5708,7 +7331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A23">
         <v>22</v>
       </c>
@@ -5725,7 +7348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A24">
         <v>23</v>
       </c>
@@ -5742,7 +7365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A25">
         <v>24</v>
       </c>
@@ -5759,7 +7382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A26">
         <v>25</v>
       </c>
@@ -5776,7 +7399,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A27">
         <v>26</v>
       </c>
@@ -5793,7 +7416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A28">
         <v>27</v>
       </c>
@@ -5810,7 +7433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A29">
         <v>28</v>
       </c>
@@ -5827,7 +7450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A30">
         <v>29</v>
       </c>
@@ -5844,7 +7467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A31">
         <v>30</v>
       </c>
@@ -5861,7 +7484,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A32">
         <v>31</v>
       </c>
@@ -5878,7 +7501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A33">
         <v>32</v>
       </c>
@@ -5895,7 +7518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A34">
         <v>33</v>
       </c>
@@ -5912,7 +7535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A35">
         <v>34</v>
       </c>
@@ -5929,7 +7552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A36">
         <v>35</v>
       </c>
@@ -5946,7 +7569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A37">
         <v>36</v>
       </c>
@@ -5963,7 +7586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A38">
         <v>37</v>
       </c>
@@ -5980,7 +7603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A39">
         <v>38</v>
       </c>
@@ -5997,7 +7620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A40">
         <v>39</v>
       </c>
@@ -6014,7 +7637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A41">
         <v>40</v>
       </c>
@@ -6031,7 +7654,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A42">
         <v>41</v>
       </c>
@@ -6048,7 +7671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A43">
         <v>42</v>
       </c>
@@ -6065,7 +7688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A44">
         <v>43</v>
       </c>
@@ -6082,7 +7705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A45">
         <v>44</v>
       </c>
@@ -6099,7 +7722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A46">
         <v>45</v>
       </c>
@@ -6116,7 +7739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A47">
         <v>46</v>
       </c>
@@ -6133,7 +7756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A48">
         <v>47</v>
       </c>
@@ -6150,7 +7773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A49">
         <v>48</v>
       </c>
@@ -6167,7 +7790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A50">
         <v>49</v>
       </c>
@@ -6184,7 +7807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A51">
         <v>50</v>
       </c>
@@ -6201,7 +7824,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A52">
         <v>51</v>
       </c>
@@ -6218,7 +7841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A53">
         <v>52</v>
       </c>
@@ -6235,7 +7858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A54">
         <v>53</v>
       </c>
@@ -6252,7 +7875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A55">
         <v>54</v>
       </c>
@@ -6269,7 +7892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A56">
         <v>55</v>
       </c>
@@ -6286,7 +7909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A57">
         <v>56</v>
       </c>
@@ -6303,7 +7926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A58">
         <v>57</v>
       </c>
@@ -6320,7 +7943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A59">
         <v>58</v>
       </c>
@@ -6337,7 +7960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A60">
         <v>59</v>
       </c>
@@ -6354,7 +7977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A61">
         <v>60</v>
       </c>
@@ -6371,7 +7994,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A62">
         <v>61</v>
       </c>
@@ -6388,7 +8011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A63">
         <v>62</v>
       </c>
@@ -6405,7 +8028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A64">
         <v>63</v>
       </c>
@@ -6422,7 +8045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A65">
         <v>64</v>
       </c>
@@ -6439,7 +8062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A66">
         <v>65</v>
       </c>
@@ -6456,7 +8079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A67">
         <v>66</v>
       </c>
@@ -6473,7 +8096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A68">
         <v>67</v>
       </c>
@@ -6490,7 +8113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A69">
         <v>68</v>
       </c>
@@ -6507,7 +8130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A70">
         <v>69</v>
       </c>
@@ -6524,7 +8147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A71">
         <v>70</v>
       </c>
@@ -6541,7 +8164,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A72">
         <v>71</v>
       </c>
@@ -6558,7 +8181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A73">
         <v>72</v>
       </c>
@@ -6575,7 +8198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A74">
         <v>73</v>
       </c>
@@ -6592,7 +8215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A75">
         <v>74</v>
       </c>
@@ -6609,7 +8232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A76">
         <v>75</v>
       </c>
@@ -6626,7 +8249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A77">
         <v>76</v>
       </c>
@@ -6643,7 +8266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A78">
         <v>77</v>
       </c>
@@ -6660,7 +8283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A79">
         <v>78</v>
       </c>
@@ -6677,7 +8300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A80">
         <v>79</v>
       </c>
@@ -6694,7 +8317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A81">
         <v>80</v>
       </c>
@@ -6711,7 +8334,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A82">
         <v>81</v>
       </c>
@@ -6728,7 +8351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A83">
         <v>82</v>
       </c>
@@ -6745,7 +8368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A84">
         <v>83</v>
       </c>
@@ -6762,7 +8385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A85">
         <v>84</v>
       </c>
@@ -6779,7 +8402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A86">
         <v>85</v>
       </c>
@@ -6796,7 +8419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A87">
         <v>86</v>
       </c>
@@ -6813,7 +8436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A88">
         <v>87</v>
       </c>
@@ -6830,7 +8453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A89">
         <v>88</v>
       </c>
@@ -6847,7 +8470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A90">
         <v>89</v>
       </c>
@@ -6864,7 +8487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A91">
         <v>90</v>
       </c>
@@ -6881,7 +8504,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A92">
         <v>91</v>
       </c>
@@ -6898,7 +8521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A93">
         <v>92</v>
       </c>
@@ -6915,7 +8538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A94">
         <v>93</v>
       </c>
@@ -6932,7 +8555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A95">
         <v>94</v>
       </c>
@@ -6949,7 +8572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A96">
         <v>95</v>
       </c>
@@ -6966,7 +8589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A97">
         <v>96</v>
       </c>
@@ -6983,7 +8606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A98">
         <v>97</v>
       </c>
@@ -7000,7 +8623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A99">
         <v>98</v>
       </c>
@@ -7017,7 +8640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A100">
         <v>99</v>
       </c>
@@ -7034,7 +8657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A101">
         <v>100</v>
       </c>
@@ -7062,15 +8685,15 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED9894AF-30A9-4679-8E69-895319B0949F}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.7"/>
   <cols>
-    <col min="1" max="1" width="16.59765625" customWidth="1"/>
-    <col min="2" max="2" width="14.3984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.625" customWidth="1"/>
+    <col min="2" max="2" width="14.375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A1" t="s">
         <v>38</v>
       </c>
@@ -7081,7 +8704,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -7092,58 +8715,124 @@
         <v>43</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B3" t="s">
         <v>42</v>
       </c>
       <c r="C3" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A4" t="s">
-        <v>103</v>
+        <v>168</v>
       </c>
       <c r="B4" t="s">
         <v>42</v>
       </c>
       <c r="C4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A5" t="s">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="B5" t="s">
         <v>42</v>
       </c>
       <c r="C5" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A6" t="s">
-        <v>138</v>
+        <v>170</v>
       </c>
       <c r="B6" t="s">
         <v>42</v>
       </c>
       <c r="C6" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A7" t="s">
-        <v>139</v>
+        <v>174</v>
       </c>
       <c r="B7" t="s">
         <v>42</v>
       </c>
       <c r="C7" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A9" t="s">
+        <v>102</v>
+      </c>
+      <c r="B9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A10" t="s">
+        <v>103</v>
+      </c>
+      <c r="B10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A11" t="s">
+        <v>136</v>
+      </c>
+      <c r="B11" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A12" t="s">
+        <v>137</v>
+      </c>
+      <c r="B12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A13" t="s">
+        <v>175</v>
+      </c>
+      <c r="B13" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" t="s">
         <v>44</v>
       </c>
     </row>
@@ -7159,15 +8848,15 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F8655EA-A40E-4922-BEBE-C6CE0494F654}">
   <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.7"/>
   <cols>
-    <col min="1" max="1" width="16.59765625" customWidth="1"/>
-    <col min="2" max="2" width="11.59765625" customWidth="1"/>
-    <col min="3" max="3" width="16.3984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.19921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.625" customWidth="1"/>
+    <col min="2" max="2" width="11.625" customWidth="1"/>
+    <col min="3" max="3" width="16.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.1875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.7">
       <c r="A1" t="s">
         <v>38</v>
       </c>
@@ -7175,10 +8864,10 @@
         <v>45</v>
       </c>
       <c r="C1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -7193,16 +8882,16 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{574776B9-E77C-4F72-80E8-6DED74B2B2EB}">
   <dimension ref="A1:E13"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.7"/>
   <cols>
     <col min="1" max="1" width="6.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.59765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.3984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.19921875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.1875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7213,13 +8902,13 @@
         <v>45</v>
       </c>
       <c r="D1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E1" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A2" t="s">
         <v>46</v>
       </c>
@@ -7233,7 +8922,7 @@
         <v>9999</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A3" t="s">
         <v>47</v>
       </c>
@@ -7247,7 +8936,7 @@
         <v>9999</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A4" t="s">
         <v>48</v>
       </c>
@@ -7264,7 +8953,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A5" t="s">
         <v>49</v>
       </c>
@@ -7281,7 +8970,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A6" t="s">
         <v>50</v>
       </c>
@@ -7298,7 +8987,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A7" t="s">
         <v>49</v>
       </c>
@@ -7315,7 +9004,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A8" t="s">
         <v>46</v>
       </c>
@@ -7329,7 +9018,7 @@
         <v>9999</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A9" t="s">
         <v>50</v>
       </c>
@@ -7346,7 +9035,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A10" t="s">
         <v>50</v>
       </c>
@@ -7363,7 +9052,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A11" t="s">
         <v>47</v>
       </c>
@@ -7377,7 +9066,7 @@
         <v>9999</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A12" t="s">
         <v>46</v>
       </c>
@@ -7391,7 +9080,7 @@
         <v>9999</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -7409,18 +9098,18 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DC603D6-2C96-4006-AE42-9221D8B477BE}">
-  <dimension ref="A1:H11"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:H21"/>
+  <sheetFormatPr defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.7"/>
   <cols>
-    <col min="1" max="1" width="17.09765625" customWidth="1"/>
-    <col min="2" max="2" width="8.19921875" customWidth="1"/>
-    <col min="3" max="3" width="16.59765625" customWidth="1"/>
-    <col min="4" max="4" width="10.3984375" customWidth="1"/>
-    <col min="5" max="5" width="10.59765625" customWidth="1"/>
-    <col min="6" max="6" width="18.8984375" customWidth="1"/>
+    <col min="1" max="1" width="17.125" customWidth="1"/>
+    <col min="2" max="2" width="8.1875" customWidth="1"/>
+    <col min="3" max="3" width="16.625" customWidth="1"/>
+    <col min="4" max="4" width="10.375" customWidth="1"/>
+    <col min="5" max="5" width="10.625" customWidth="1"/>
+    <col min="6" max="6" width="18.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7446,9 +9135,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.7">
       <c r="A2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -7463,7 +9152,7 @@
         <v>20</v>
       </c>
       <c r="F2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -7472,9 +9161,9 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.7">
       <c r="A3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -7489,7 +9178,7 @@
         <v>30</v>
       </c>
       <c r="F3" t="s">
-        <v>131</v>
+        <v>206</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -7498,9 +9187,9 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.7">
       <c r="A4" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -7515,7 +9204,7 @@
         <v>40</v>
       </c>
       <c r="F4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -7524,15 +9213,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.7">
       <c r="A5" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D5">
         <v>11</v>
@@ -7541,7 +9230,7 @@
         <v>20</v>
       </c>
       <c r="F5" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -7550,15 +9239,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.7">
       <c r="A6" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B6">
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D6">
         <v>21</v>
@@ -7567,7 +9256,7 @@
         <v>30</v>
       </c>
       <c r="F6" t="s">
-        <v>159</v>
+        <v>208</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -7576,15 +9265,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.7">
       <c r="A7" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B7">
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D7">
         <v>31</v>
@@ -7593,7 +9282,7 @@
         <v>40</v>
       </c>
       <c r="F7" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -7602,15 +9291,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.7">
       <c r="A8" t="s">
-        <v>126</v>
+        <v>196</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>103</v>
+        <v>168</v>
       </c>
       <c r="D8">
         <v>11</v>
@@ -7618,68 +9307,77 @@
       <c r="E8">
         <v>20</v>
       </c>
+      <c r="F8" t="s">
+        <v>202</v>
+      </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.7">
       <c r="A9" t="s">
-        <v>127</v>
+        <v>197</v>
       </c>
       <c r="B9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9" t="s">
-        <v>104</v>
+        <v>168</v>
       </c>
       <c r="D9">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="E9">
-        <v>20</v>
+        <v>30</v>
+      </c>
+      <c r="F9" t="s">
+        <v>207</v>
       </c>
       <c r="G9">
         <v>0</v>
       </c>
       <c r="H9">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.7">
       <c r="A10" t="s">
-        <v>140</v>
+        <v>198</v>
       </c>
       <c r="B10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C10" t="s">
-        <v>138</v>
+        <v>168</v>
       </c>
       <c r="D10">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="E10">
-        <v>20</v>
+        <v>40</v>
+      </c>
+      <c r="F10" t="s">
+        <v>203</v>
       </c>
       <c r="G10">
         <v>0</v>
       </c>
       <c r="H10">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.7">
       <c r="A11" t="s">
-        <v>141</v>
+        <v>199</v>
       </c>
       <c r="B11">
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>139</v>
+        <v>169</v>
       </c>
       <c r="D11">
         <v>11</v>
@@ -7687,10 +9385,249 @@
       <c r="E11">
         <v>20</v>
       </c>
+      <c r="F11" t="s">
+        <v>204</v>
+      </c>
       <c r="G11">
         <v>0</v>
       </c>
       <c r="H11">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.7">
+      <c r="A12" t="s">
+        <v>200</v>
+      </c>
+      <c r="B12">
+        <v>2</v>
+      </c>
+      <c r="C12" t="s">
+        <v>167</v>
+      </c>
+      <c r="D12">
+        <v>21</v>
+      </c>
+      <c r="E12">
+        <v>30</v>
+      </c>
+      <c r="F12" t="s">
+        <v>209</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.7">
+      <c r="A13" t="s">
+        <v>201</v>
+      </c>
+      <c r="B13">
+        <v>3</v>
+      </c>
+      <c r="C13" t="s">
+        <v>167</v>
+      </c>
+      <c r="D13">
+        <v>31</v>
+      </c>
+      <c r="E13">
+        <v>40</v>
+      </c>
+      <c r="F13" t="s">
+        <v>205</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.7">
+      <c r="A14" t="s">
+        <v>193</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14" t="s">
+        <v>189</v>
+      </c>
+      <c r="D14">
+        <v>11</v>
+      </c>
+      <c r="E14">
+        <v>20</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.7">
+      <c r="A15" t="s">
+        <v>194</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15" t="s">
+        <v>190</v>
+      </c>
+      <c r="D15">
+        <v>11</v>
+      </c>
+      <c r="E15">
+        <v>20</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.7">
+      <c r="A16" t="s">
+        <v>195</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16" t="s">
+        <v>191</v>
+      </c>
+      <c r="D16">
+        <v>11</v>
+      </c>
+      <c r="E16">
+        <v>20</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.7">
+      <c r="A17" t="s">
+        <v>125</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17" t="s">
+        <v>102</v>
+      </c>
+      <c r="D17">
+        <v>11</v>
+      </c>
+      <c r="E17">
+        <v>20</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.7">
+      <c r="A18" t="s">
+        <v>126</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18" t="s">
+        <v>103</v>
+      </c>
+      <c r="D18">
+        <v>11</v>
+      </c>
+      <c r="E18">
+        <v>20</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.7">
+      <c r="A19" t="s">
+        <v>138</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19" t="s">
+        <v>136</v>
+      </c>
+      <c r="D19">
+        <v>11</v>
+      </c>
+      <c r="E19">
+        <v>20</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.7">
+      <c r="A20" t="s">
+        <v>139</v>
+      </c>
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20" t="s">
+        <v>137</v>
+      </c>
+      <c r="D20">
+        <v>11</v>
+      </c>
+      <c r="E20">
+        <v>20</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.7">
+      <c r="A21" t="s">
+        <v>192</v>
+      </c>
+      <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21" t="s">
+        <v>137</v>
+      </c>
+      <c r="D21">
+        <v>11</v>
+      </c>
+      <c r="E21">
+        <v>20</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
         <v>-1</v>
       </c>
     </row>
@@ -7705,17 +9642,17 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FB3B4E8-C5C7-487A-BB3C-0105F4AA5D23}">
-  <dimension ref="A1:F15"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.7"/>
   <cols>
-    <col min="1" max="1" width="20.3984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="24.19921875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.19921875" customWidth="1"/>
-    <col min="5" max="5" width="13.8984375" customWidth="1"/>
-    <col min="6" max="6" width="15.59765625" customWidth="1"/>
+    <col min="1" max="1" width="20.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="24.1875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.1875" customWidth="1"/>
+    <col min="5" max="5" width="13.875" customWidth="1"/>
+    <col min="6" max="6" width="15.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7723,10 +9660,10 @@
         <v>38</v>
       </c>
       <c r="C1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E1" t="s">
         <v>86</v>
@@ -7735,15 +9672,15 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -7752,18 +9689,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B3" t="s">
         <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -7772,18 +9709,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B4" t="s">
         <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -7792,18 +9729,18 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A5" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B5" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C5" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="D5" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -7812,18 +9749,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A6" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B6" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C6" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -7832,18 +9769,18 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B7" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C7" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D7" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -7852,58 +9789,58 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A8" t="s">
-        <v>53</v>
+        <v>224</v>
       </c>
       <c r="B8" t="s">
-        <v>103</v>
+        <v>168</v>
       </c>
       <c r="C8" t="s">
-        <v>124</v>
+        <v>211</v>
       </c>
       <c r="D8" t="s">
-        <v>119</v>
+        <v>212</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A9" t="s">
-        <v>115</v>
+        <v>225</v>
       </c>
       <c r="B9" t="s">
-        <v>125</v>
+        <v>169</v>
       </c>
       <c r="C9" t="s">
-        <v>123</v>
+        <v>213</v>
       </c>
       <c r="D9" t="s">
-        <v>120</v>
+        <v>214</v>
       </c>
       <c r="E9">
         <v>0</v>
       </c>
       <c r="F9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A10" t="s">
-        <v>53</v>
+        <v>226</v>
       </c>
       <c r="B10" t="s">
-        <v>138</v>
+        <v>189</v>
       </c>
       <c r="C10" t="s">
-        <v>124</v>
+        <v>215</v>
       </c>
       <c r="D10" t="s">
-        <v>119</v>
+        <v>216</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -7912,28 +9849,148 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A11" t="s">
-        <v>115</v>
+        <v>227</v>
       </c>
       <c r="B11" t="s">
-        <v>142</v>
+        <v>190</v>
       </c>
       <c r="C11" t="s">
+        <v>217</v>
+      </c>
+      <c r="D11" t="s">
+        <v>218</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.7">
+      <c r="A12" t="s">
+        <v>228</v>
+      </c>
+      <c r="B12" t="s">
+        <v>191</v>
+      </c>
+      <c r="C12" t="s">
+        <v>219</v>
+      </c>
+      <c r="D12" t="s">
+        <v>220</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.7">
+      <c r="A13" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" t="s">
+        <v>102</v>
+      </c>
+      <c r="C13" t="s">
         <v>123</v>
       </c>
-      <c r="D11" t="s">
-        <v>120</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
+      <c r="D13" t="s">
+        <v>118</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.7">
+      <c r="A14" t="s">
+        <v>114</v>
+      </c>
+      <c r="B14" t="s">
+        <v>124</v>
+      </c>
+      <c r="C14" t="s">
+        <v>122</v>
+      </c>
+      <c r="D14" t="s">
+        <v>119</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="E15" s="2"/>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.7">
+      <c r="A15" t="s">
+        <v>53</v>
+      </c>
+      <c r="B15" t="s">
+        <v>136</v>
+      </c>
+      <c r="C15" t="s">
+        <v>123</v>
+      </c>
+      <c r="D15" t="s">
+        <v>118</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.7">
+      <c r="A16" t="s">
+        <v>114</v>
+      </c>
+      <c r="B16" t="s">
+        <v>140</v>
+      </c>
+      <c r="C16" t="s">
+        <v>122</v>
+      </c>
+      <c r="D16" t="s">
+        <v>119</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.7">
+      <c r="A17" t="s">
+        <v>114</v>
+      </c>
+      <c r="B17" t="s">
+        <v>210</v>
+      </c>
+      <c r="C17" t="s">
+        <v>122</v>
+      </c>
+      <c r="D17" t="s">
+        <v>119</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.7">
+      <c r="E21" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
